--- a/الخدمات.xlsx
+++ b/الخدمات.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a843af4fc71c607/Desktop/JavaScript codes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3169" documentId="11_6D1415C555E27CE26E339E56ADDC14C75C28AAF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5460B452-1C81-41FD-B34D-85B3EAE88424}"/>
+  <xr:revisionPtr revIDLastSave="3295" documentId="11_6D1415C555E27CE26E339E56ADDC14C75C28AAF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1000008D-9CCA-4D56-824E-B608BFB5304F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="معلومات الخدمات" sheetId="1" r:id="rId1"/>
@@ -36,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="506">
   <si>
     <t>ت.</t>
   </si>
@@ -1525,13 +1547,43 @@
   </si>
   <si>
     <t>شهداء كورونا</t>
+  </si>
+  <si>
+    <t>منح شهادة الاعتماد- جهات التفتيش</t>
+  </si>
+  <si>
+    <t>جهات التفتيش</t>
+  </si>
+  <si>
+    <t>خدمة الجرحى المتقاعدين لمنتسبي وزارة الدفاع</t>
+  </si>
+  <si>
+    <t>الجرحى المتقاعدين</t>
+  </si>
+  <si>
+    <t>التقديم للعمل بصفة مرشد/ة لموسم الحج 1448 هـ</t>
+  </si>
+  <si>
+    <t>بصفة مرشد/ة</t>
+  </si>
+  <si>
+    <t>تقديم طلب إلكتروني للحصول عل خدمات منصة إنجاز الرقمية - دوائر ديوان الوقف الشيعي</t>
+  </si>
+  <si>
+    <t>إنجاز رقمية</t>
+  </si>
+  <si>
+    <t>التقديم للاعتراض على عدم القبول على فريضة الحج للمتقدمين الكترونيا من المشمولين بقانون مؤسسة السجناء السياسيين لسنة 2027</t>
+  </si>
+  <si>
+    <t>تقديم على اعتراض</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1565,16 +1617,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor theme="8" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor theme="8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1713,12 +1784,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1796,22 +1882,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="58">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="57">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3252,39 +3355,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G230" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G230">
-    <sortCondition ref="B2:B230"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G235" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G234">
+    <sortCondition ref="B2:B234"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{20FD99FD-87DB-4DD1-989A-014AAE8F25F6}" name="ت." dataDxfId="54" totalsRowDxfId="53">
+    <tableColumn id="1" xr3:uid="{20FD99FD-87DB-4DD1-989A-014AAE8F25F6}" name="ت." dataDxfId="53" totalsRowDxfId="52">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F323E4AC-F323-4F97-9904-326D9949B165}" name="رقم الخدمة" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{58A3CC8C-66BF-4DA6-B0EF-C7F43089C5C0}" name="اسم الخدمة" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{176DB514-0824-46BC-9146-CAA89D7A742F}" name="جهة الخدمة" dataDxfId="48" totalsRowDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{E4173C63-A839-4611-8E53-7B3AE2F439DB}" name="نوع الجهة" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{C01A4E12-3E16-4DE9-86B3-69F70894487E}" name="نوع العمل" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{3481871F-BF9F-4C45-AC54-67A9AF362483}" name="اسم الملف" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{F323E4AC-F323-4F97-9904-326D9949B165}" name="رقم الخدمة" dataDxfId="51" totalsRowDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{58A3CC8C-66BF-4DA6-B0EF-C7F43089C5C0}" name="اسم الخدمة" dataDxfId="49" totalsRowDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{176DB514-0824-46BC-9146-CAA89D7A742F}" name="جهة الخدمة" dataDxfId="47" totalsRowDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{E4173C63-A839-4611-8E53-7B3AE2F439DB}" name="نوع الجهة" dataDxfId="45" totalsRowDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{C01A4E12-3E16-4DE9-86B3-69F70894487E}" name="نوع العمل" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{3481871F-BF9F-4C45-AC54-67A9AF362483}" name="اسم الملف" dataDxfId="41" totalsRowDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="40" dataDxfId="38" totalsRowDxfId="37" headerRowBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="39" dataDxfId="37" totalsRowDxfId="36" headerRowBorderDxfId="38">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F2:I8">
     <sortCondition ref="G2:G8"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FDC31943-D832-4BCF-8A6F-51F74847839D}" name="ت." dataDxfId="36" totalsRowDxfId="35">
+    <tableColumn id="1" xr3:uid="{FDC31943-D832-4BCF-8A6F-51F74847839D}" name="ت." dataDxfId="35" totalsRowDxfId="34">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D6F61CFE-6FB5-4088-802C-280AB03DDC3F}" name="نوع الجهة" totalsRowLabel="المجموع" dataDxfId="34" totalsRowDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{819F64F0-7B30-437C-8552-96E1BA009158}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
+    <tableColumn id="2" xr3:uid="{D6F61CFE-6FB5-4088-802C-280AB03DDC3F}" name="نوع الجهة" totalsRowLabel="المجموع" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{819F64F0-7B30-437C-8552-96E1BA009158}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
       <calculatedColumnFormula>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D928E8D0-BE48-4700-B3FA-A3A0C6ED8D95}" name="النسبة المئوية" dataDxfId="30" totalsRowDxfId="29" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{D928E8D0-BE48-4700-B3FA-A3A0C6ED8D95}" name="النسبة المئوية" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Percent">
       <calculatedColumnFormula>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3293,19 +3396,19 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D42" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D42" totalsRowCount="1" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D41">
     <sortCondition ref="B2:B41"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{04CB5523-1DF6-4CA0-AC24-1D21F85D9F94}" name="ت." dataDxfId="23" totalsRowDxfId="22">
+    <tableColumn id="1" xr3:uid="{04CB5523-1DF6-4CA0-AC24-1D21F85D9F94}" name="ت." dataDxfId="22" totalsRowDxfId="21">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{966ACB29-C086-4C8E-BD62-D0F9ECCCA301}" name="اسم الجهة" totalsRowLabel="المجموع" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{E47A3AE0-B7A7-44F8-8FA6-8FA757A3066F}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18">
+    <tableColumn id="2" xr3:uid="{966ACB29-C086-4C8E-BD62-D0F9ECCCA301}" name="اسم الجهة" totalsRowLabel="المجموع" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{E47A3AE0-B7A7-44F8-8FA6-8FA757A3066F}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="17">
       <calculatedColumnFormula>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0D34DEDD-061D-44F4-9DA6-86D41E4BDDB7}" name="النسبة المئوية" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{0D34DEDD-061D-44F4-9DA6-86D41E4BDDB7}" name="النسبة المئوية" totalsRowFunction="sum" dataDxfId="16" totalsRowDxfId="15" dataCellStyle="Percent">
       <calculatedColumnFormula>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3314,16 +3417,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="10" totalsRowDxfId="9">
+    <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="9" totalsRowDxfId="8">
       <calculatedColumnFormula>ROW()-11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4A8E3EC9-46C6-46A2-85BB-E7D02B7ABF90}" name="نوع العمل" totalsRowLabel="المجموع" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{140AD779-6235-4A33-848F-7CF18BA55E33}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="5">
+    <tableColumn id="2" xr3:uid="{4A8E3EC9-46C6-46A2-85BB-E7D02B7ABF90}" name="نوع العمل" totalsRowLabel="المجموع" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{140AD779-6235-4A33-848F-7CF18BA55E33}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4">
       <calculatedColumnFormula>COUNTIF(Table1[نوع العمل],Table4[[#This Row],[نوع العمل]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CD921388-F9B8-4CDD-A07C-FBB8C0ABF589}" name="النسبة المئوية" dataDxfId="4" totalsRowDxfId="3" dataCellStyle="Percent">
+    <tableColumn id="4" xr3:uid="{CD921388-F9B8-4CDD-A07C-FBB8C0ABF589}" name="النسبة المئوية" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Percent">
       <calculatedColumnFormula>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3594,7 +3697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G230"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
@@ -3631,7 +3734,7 @@
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A2:A65" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -3655,7 +3758,7 @@
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B3" s="3">
@@ -3679,7 +3782,7 @@
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="3">
@@ -3703,7 +3806,7 @@
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="3">
@@ -3727,7 +3830,7 @@
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="3">
@@ -3751,7 +3854,7 @@
     </row>
     <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="3">
@@ -3775,7 +3878,7 @@
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="3">
@@ -3799,7 +3902,7 @@
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="3">
@@ -3823,7 +3926,7 @@
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="3">
@@ -3847,7 +3950,7 @@
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="3">
@@ -3871,7 +3974,7 @@
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="3">
@@ -3895,41 +3998,41 @@
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>10508</v>
+        <v>10478</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>271</v>
+        <v>502</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>88</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>272</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>10509</v>
+        <v>10508</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>480</v>
+        <v>271</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>7</v>
@@ -3938,22 +4041,22 @@
         <v>88</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>481</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>10514</v>
+        <v>10509</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>37</v>
+        <v>480</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>7</v>
@@ -3962,43 +4065,43 @@
         <v>88</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>199</v>
+        <v>481</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>10532</v>
+        <v>10514</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G16" s="1">
-        <v>10532</v>
+      <c r="G16" s="1" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>10539</v>
+        <v>10532</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>79</v>
@@ -4010,19 +4113,19 @@
         <v>88</v>
       </c>
       <c r="G17" s="1">
-        <v>10539</v>
+        <v>10532</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>10541</v>
+        <v>10539</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>79</v>
@@ -4034,67 +4137,67 @@
         <v>88</v>
       </c>
       <c r="G18" s="1">
-        <v>10541</v>
+        <v>10539</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>10562</v>
+        <v>10541</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>192</v>
+      <c r="G19" s="1">
+        <v>10541</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>10565</v>
+        <v>10562</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G20" s="1">
-        <v>10565</v>
+      <c r="G20" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>10568</v>
+        <v>10565</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>79</v>
@@ -4106,46 +4209,46 @@
         <v>88</v>
       </c>
       <c r="G21" s="1">
-        <v>10568</v>
+        <v>10565</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>10579</v>
+        <v>10568</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>240</v>
+      <c r="G22" s="1">
+        <v>10568</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>10603</v>
+        <v>10579</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>444</v>
+        <v>97</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>7</v>
@@ -4154,43 +4257,43 @@
         <v>88</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>445</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>10611</v>
+        <v>10603</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>145</v>
+        <v>444</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G24" s="1">
-        <v>10611</v>
+      <c r="G24" s="1" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>10630</v>
+        <v>10611</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>79</v>
@@ -4202,46 +4305,46 @@
         <v>88</v>
       </c>
       <c r="G25" s="1">
-        <v>10630</v>
+        <v>10611</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>10648</v>
+        <v>10630</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>232</v>
+      <c r="G26" s="1">
+        <v>10630</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>10664</v>
+        <v>10648</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>325</v>
+        <v>130</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>7</v>
@@ -4249,167 +4352,167 @@
       <c r="F27" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G27" s="1">
-        <v>10664</v>
+      <c r="G27" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>10675</v>
+        <v>10664</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>38</v>
+        <v>325</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>200</v>
+        <v>88</v>
+      </c>
+      <c r="G28" s="1">
+        <v>10664</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>10688</v>
+        <v>10675</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G29" s="1">
-        <v>10688</v>
+        <v>89</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>10712</v>
+        <v>10688</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>360</v>
+        <v>152</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>361</v>
+      <c r="G30" s="1">
+        <v>10688</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>10715</v>
+        <v>10712</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>63</v>
+        <v>360</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>238</v>
+        <v>361</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10727</v>
+        <v>10715</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>163</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>10730</v>
+        <v>10727</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>10756</v>
+        <v>10730</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>403</v>
+        <v>362</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>7</v>
@@ -4418,22 +4521,22 @@
         <v>88</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>404</v>
+        <v>363</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>10780</v>
+        <v>10756</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>65</v>
+        <v>403</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>7</v>
@@ -4442,163 +4545,163 @@
         <v>88</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>186</v>
+        <v>404</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B36" s="3">
-        <v>10876</v>
+        <v>10780</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>430</v>
+        <v>66</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>321</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B37" s="3">
-        <v>10884</v>
+        <v>10876</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>47</v>
+        <v>320</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>46</v>
+        <v>430</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>231</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B38" s="3">
-        <v>10913</v>
+        <v>10884</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B39" s="3">
-        <v>10928</v>
+        <v>10913</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>235</v>
+        <v>30</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B40" s="3">
-        <v>10930</v>
+        <v>10928</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B41" s="3">
-        <v>10935</v>
+        <v>10930</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>233</v>
+        <v>161</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>234</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B42" s="3">
-        <v>10947</v>
+        <v>10935</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>375</v>
+        <v>233</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>46</v>
@@ -4610,22 +4713,22 @@
         <v>88</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>376</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B43" s="3">
-        <v>10974</v>
+        <v>10947</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>93</v>
+        <v>375</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>7</v>
@@ -4634,22 +4737,22 @@
         <v>88</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>215</v>
+        <v>376</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B44" s="3">
-        <v>10979</v>
+        <v>10974</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>7</v>
@@ -4658,43 +4761,43 @@
         <v>88</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B45" s="3">
-        <v>10987</v>
+        <v>10979</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>170</v>
+        <v>261</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B46" s="3">
-        <v>10995</v>
+        <v>10987</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>22</v>
@@ -4706,70 +4809,70 @@
         <v>88</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B47" s="3">
-        <v>21020</v>
+        <v>10995</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>33</v>
+        <v>155</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>33</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B48" s="3">
-        <v>21058</v>
+        <v>21020</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>294</v>
+        <v>33</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>187</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B49" s="3">
-        <v>21063</v>
+        <v>21058</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>117</v>
+        <v>294</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>7</v>
@@ -4778,118 +4881,118 @@
         <v>88</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B50" s="3">
-        <v>21064</v>
+        <v>21063</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B51" s="3">
-        <v>21067</v>
+        <v>21064</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>154</v>
+        <v>11</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B52" s="3">
-        <v>21070</v>
+        <v>21067</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B53" s="3">
-        <v>21071</v>
+        <v>21070</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B54" s="3">
-        <v>21075</v>
+        <v>21071</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>476</v>
+        <v>36</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>7</v>
@@ -4898,142 +5001,142 @@
         <v>88</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>477</v>
+        <v>201</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B55" s="3">
-        <v>21076</v>
+        <v>21075</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>160</v>
+        <v>476</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G55" s="1">
-        <v>21076</v>
+      <c r="G55" s="1" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B56" s="3">
-        <v>21078</v>
+        <v>21076</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>179</v>
+      <c r="G56" s="1">
+        <v>21076</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B57" s="3">
-        <v>21093</v>
+        <v>21078</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B58" s="3">
-        <v>21097</v>
+        <v>21093</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B59" s="3">
-        <v>21098</v>
+        <v>21097</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>301</v>
+        <v>42</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>302</v>
+        <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B60" s="3">
-        <v>21102</v>
+        <v>21098</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>86</v>
+        <v>301</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>7</v>
@@ -5042,70 +5145,70 @@
         <v>88</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>229</v>
+        <v>302</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B61" s="3">
-        <v>21116</v>
+        <v>21102</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>266</v>
+        <v>86</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>267</v>
+        <v>229</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B62" s="3">
-        <v>21126</v>
+        <v>21116</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>69</v>
+        <v>266</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>188</v>
+        <v>267</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="B63" s="3">
-        <v>21151</v>
+        <v>21126</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>7</v>
@@ -5114,67 +5217,67 @@
         <v>88</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B64" s="3">
-        <v>21179</v>
+        <v>21151</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B65" s="3">
-        <v>21184</v>
+        <v>21179</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>260</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A66:A129" si="1">ROW()-1</f>
         <v>65</v>
       </c>
       <c r="B66" s="3">
-        <v>21185</v>
+        <v>21184</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>24</v>
@@ -5186,163 +5289,163 @@
         <v>89</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
       <c r="B67" s="3">
-        <v>21186</v>
+        <v>21185</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>39</v>
+        <v>258</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
       <c r="B68" s="3">
-        <v>21193</v>
+        <v>21186</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>159</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="B69" s="3">
-        <v>21195</v>
+        <v>21193</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>69</v>
       </c>
       <c r="B70" s="3">
-        <v>21196</v>
+        <v>21195</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="B71" s="3">
-        <v>21209</v>
+        <v>21196</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>71</v>
       </c>
       <c r="B72" s="3">
-        <v>21216</v>
+        <v>21209</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>436</v>
+        <v>92</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>437</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="B73" s="3">
-        <v>21218</v>
+        <v>21216</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>146</v>
+        <v>436</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>15</v>
@@ -5354,142 +5457,142 @@
         <v>88</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>168</v>
+        <v>437</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="B74" s="3">
-        <v>21219</v>
+        <v>21218</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>259</v>
+        <v>168</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="B75" s="3">
-        <v>21220</v>
+        <v>21219</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="B76" s="3">
-        <v>21222</v>
+        <v>21220</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>165</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="B77" s="3">
-        <v>21226</v>
+        <v>21222</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>255</v>
+        <v>75</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="B78" s="3">
-        <v>21228</v>
+        <v>21226</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>67</v>
+        <v>255</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="B79" s="3">
-        <v>21241</v>
+        <v>21228</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>7</v>
@@ -5498,70 +5601,70 @@
         <v>88</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>79</v>
       </c>
       <c r="B80" s="3">
-        <v>21242</v>
+        <v>21241</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>176</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="B81" s="3">
-        <v>21247</v>
+        <v>21242</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>81</v>
       </c>
       <c r="B82" s="3">
-        <v>21261</v>
+        <v>21247</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>284</v>
+        <v>44</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>7</v>
@@ -5570,70 +5673,70 @@
         <v>88</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>285</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="B83" s="3">
-        <v>21264</v>
+        <v>21261</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>71</v>
+        <v>284</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>183</v>
+        <v>285</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>83</v>
       </c>
       <c r="B84" s="3">
-        <v>21305</v>
+        <v>21264</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="B85" s="3">
-        <v>21311</v>
+        <v>21305</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>7</v>
@@ -5642,67 +5745,67 @@
         <v>88</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>96</v>
+        <v>220</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="B86" s="3">
-        <v>21312</v>
+        <v>21311</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>245</v>
+        <v>96</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="B87" s="3">
-        <v>21323</v>
+        <v>21312</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>297</v>
+        <v>23</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>87</v>
       </c>
       <c r="B88" s="3">
-        <v>21324</v>
+        <v>21323</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>12</v>
@@ -5714,22 +5817,22 @@
         <v>88</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="B89" s="3">
-        <v>21325</v>
+        <v>21324</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>17</v>
+        <v>295</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>10</v>
@@ -5738,115 +5841,115 @@
         <v>88</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>178</v>
+        <v>296</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="B90" s="3">
-        <v>21331</v>
+        <v>21325</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>269</v>
+        <v>17</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>270</v>
+        <v>178</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="B91" s="3">
-        <v>21337</v>
+        <v>21331</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>32</v>
+        <v>269</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>91</v>
       </c>
       <c r="B92" s="3">
-        <v>21343</v>
+        <v>21337</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>353</v>
+        <v>32</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>354</v>
+        <v>24</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>355</v>
+        <v>265</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="B93" s="3">
-        <v>21356</v>
+        <v>21343</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>26</v>
+        <v>353</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>24</v>
+        <v>354</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>257</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>93</v>
       </c>
       <c r="B94" s="3">
-        <v>21374</v>
+        <v>21356</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>24</v>
@@ -5858,94 +5961,94 @@
         <v>89</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="B95" s="3">
-        <v>21377</v>
+        <v>21374</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="B96" s="3">
-        <v>21378</v>
+        <v>21377</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>253</v>
+        <v>202</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="B97" s="3">
-        <v>21381</v>
+        <v>21378</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="B98" s="3">
-        <v>21390</v>
+        <v>21381</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>45</v>
+        <v>151</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>7</v>
@@ -5954,22 +6057,22 @@
         <v>88</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>98</v>
       </c>
       <c r="B99" s="3">
-        <v>21391</v>
+        <v>21390</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>282</v>
+        <v>45</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>7</v>
@@ -5978,22 +6081,22 @@
         <v>88</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>283</v>
+        <v>230</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="B100" s="3">
-        <v>21395</v>
+        <v>21391</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>106</v>
+        <v>282</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>7</v>
@@ -6002,118 +6105,118 @@
         <v>88</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>222</v>
+        <v>283</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="B101" s="3">
-        <v>21404</v>
+        <v>21395</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>101</v>
       </c>
       <c r="B102" s="3">
-        <v>21405</v>
+        <v>21404</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>254</v>
+        <v>166</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>102</v>
       </c>
       <c r="B103" s="3">
-        <v>21407</v>
+        <v>21405</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>430</v>
+        <v>24</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>103</v>
       </c>
       <c r="B104" s="3">
-        <v>21409</v>
+        <v>21407</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>60</v>
+        <v>430</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="B105" s="3">
-        <v>21411</v>
+        <v>21409</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>338</v>
+        <v>59</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>7</v>
@@ -6122,19 +6225,19 @@
         <v>88</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>339</v>
+        <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="B106" s="3">
-        <v>21412</v>
+        <v>21411</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>34</v>
+        <v>338</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>35</v>
@@ -6146,19 +6249,19 @@
         <v>88</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>203</v>
+        <v>339</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>106</v>
       </c>
       <c r="B107" s="3">
-        <v>21413</v>
+        <v>21412</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>35</v>
@@ -6170,22 +6273,22 @@
         <v>88</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>107</v>
       </c>
       <c r="B108" s="3">
-        <v>21422</v>
+        <v>21413</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>442</v>
+        <v>101</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>7</v>
@@ -6194,19 +6297,19 @@
         <v>88</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>443</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
       <c r="B109" s="3">
-        <v>21424</v>
+        <v>21422</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>112</v>
+        <v>442</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>43</v>
@@ -6218,22 +6321,22 @@
         <v>88</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>112</v>
+        <v>443</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>109</v>
       </c>
       <c r="B110" s="3">
-        <v>21425</v>
+        <v>21424</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>7</v>
@@ -6242,139 +6345,139 @@
         <v>88</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="B111" s="3">
-        <v>21431</v>
+        <v>21425</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="B112" s="3">
-        <v>21433</v>
+        <v>21431</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="B113" s="3">
-        <v>21439</v>
+        <v>21433</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>113</v>
       </c>
       <c r="B114" s="3">
-        <v>21442</v>
+        <v>21439</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>114</v>
       </c>
       <c r="B115" s="3">
-        <v>21445</v>
+        <v>21442</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="B116" s="3">
-        <v>21448</v>
+        <v>21445</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>58</v>
@@ -6386,19 +6489,19 @@
         <v>89</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>116</v>
       </c>
       <c r="B117" s="3">
-        <v>21449</v>
+        <v>21448</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>58</v>
@@ -6407,169 +6510,169 @@
         <v>7</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>117</v>
       </c>
       <c r="B118" s="3">
-        <v>21451</v>
+        <v>21449</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>430</v>
+        <v>58</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>118</v>
       </c>
       <c r="B119" s="3">
-        <v>21453</v>
+        <v>21451</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>41</v>
+        <v>430</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>119</v>
       </c>
       <c r="B120" s="3">
-        <v>21454</v>
+        <v>21453</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>134</v>
+        <v>7</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="B121" s="3">
-        <v>21464</v>
+        <v>21454</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>7</v>
+        <v>134</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>205</v>
+        <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>121</v>
       </c>
       <c r="B122" s="3">
-        <v>21465</v>
+        <v>21464</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>313</v>
+        <v>153</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>314</v>
+        <v>35</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>315</v>
+        <v>205</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>122</v>
       </c>
       <c r="B123" s="3">
-        <v>21470</v>
+        <v>21465</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>109</v>
+        <v>313</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>24</v>
+        <v>314</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>249</v>
+        <v>315</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>123</v>
       </c>
       <c r="B124" s="3">
-        <v>21474</v>
+        <v>21470</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>7</v>
@@ -6578,22 +6681,22 @@
         <v>88</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>191</v>
+        <v>249</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>124</v>
       </c>
       <c r="B125" s="3">
-        <v>21476</v>
+        <v>21474</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>7</v>
@@ -6602,22 +6705,22 @@
         <v>88</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>241</v>
+        <v>191</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>125</v>
       </c>
       <c r="B126" s="3">
-        <v>21477</v>
+        <v>21476</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>7</v>
@@ -6626,22 +6729,22 @@
         <v>88</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="B127" s="3">
-        <v>21479</v>
+        <v>21477</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>417</v>
+        <v>108</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>329</v>
+        <v>24</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>7</v>
@@ -6650,19 +6753,19 @@
         <v>88</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>418</v>
+        <v>263</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="B128" s="3">
-        <v>21484</v>
+        <v>21479</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>329</v>
@@ -6674,19 +6777,19 @@
         <v>88</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>128</v>
       </c>
       <c r="B129" s="3">
-        <v>21485</v>
+        <v>21484</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>329</v>
@@ -6698,22 +6801,22 @@
         <v>88</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A130:A193" si="2">ROW()-1</f>
         <v>129</v>
       </c>
       <c r="B130" s="3">
-        <v>21488</v>
+        <v>21485</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>113</v>
+        <v>405</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>68</v>
+        <v>329</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>7</v>
@@ -6722,70 +6825,70 @@
         <v>88</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>130</v>
       </c>
       <c r="B131" s="3">
-        <v>21490</v>
+        <v>21488</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>169</v>
+        <v>244</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>131</v>
       </c>
       <c r="B132" s="3">
-        <v>21492</v>
+        <v>21490</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>243</v>
+        <v>169</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>132</v>
       </c>
       <c r="B133" s="3">
-        <v>21494</v>
+        <v>21492</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>407</v>
+        <v>116</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>329</v>
+        <v>68</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>7</v>
@@ -6794,19 +6897,19 @@
         <v>88</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>408</v>
+        <v>243</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>133</v>
       </c>
       <c r="B134" s="3">
-        <v>21495</v>
+        <v>21494</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>329</v>
@@ -6818,19 +6921,19 @@
         <v>88</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>134</v>
       </c>
       <c r="B135" s="3">
-        <v>21501</v>
+        <v>21495</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>329</v>
@@ -6842,22 +6945,22 @@
         <v>88</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>135</v>
       </c>
       <c r="B136" s="3">
-        <v>21502</v>
+        <v>21501</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>123</v>
+        <v>415</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>24</v>
+        <v>329</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>7</v>
@@ -6866,19 +6969,19 @@
         <v>88</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>248</v>
+        <v>416</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>136</v>
       </c>
       <c r="B137" s="3">
-        <v>21506</v>
+        <v>21502</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>246</v>
+        <v>123</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>24</v>
@@ -6890,22 +6993,22 @@
         <v>88</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="B138" s="3">
-        <v>21507</v>
+        <v>21506</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>7</v>
@@ -6914,70 +7017,70 @@
         <v>88</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>209</v>
+        <v>247</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>138</v>
       </c>
       <c r="B139" s="3">
-        <v>21509</v>
+        <v>21507</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>132</v>
+        <v>208</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>134</v>
+        <v>7</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>139</v>
       </c>
       <c r="B140" s="3">
-        <v>21511</v>
+        <v>21509</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>7</v>
+        <v>134</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>140</v>
       </c>
       <c r="B141" s="3">
-        <v>21515</v>
+        <v>21511</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>329</v>
+        <v>58</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>7</v>
@@ -6986,22 +7089,22 @@
         <v>88</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>412</v>
+        <v>214</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>141</v>
       </c>
       <c r="B142" s="3">
-        <v>21517</v>
+        <v>21515</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>135</v>
+        <v>411</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>107</v>
+        <v>329</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>7</v>
@@ -7010,67 +7113,67 @@
         <v>88</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>223</v>
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>142</v>
       </c>
       <c r="B143" s="3">
-        <v>21524</v>
+        <v>21517</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>143</v>
       </c>
       <c r="B144" s="3">
-        <v>21527</v>
+        <v>21524</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>331</v>
+        <v>128</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>329</v>
+        <v>129</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>332</v>
+        <v>173</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>144</v>
       </c>
       <c r="B145" s="3">
-        <v>21528</v>
+        <v>21527</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>329</v>
@@ -7082,22 +7185,22 @@
         <v>88</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>145</v>
       </c>
       <c r="B146" s="3">
-        <v>21553</v>
+        <v>21528</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>472</v>
+        <v>328</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>64</v>
+        <v>329</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>7</v>
@@ -7106,22 +7209,22 @@
         <v>88</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>473</v>
+        <v>330</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>146</v>
       </c>
       <c r="B147" s="3">
-        <v>21556</v>
+        <v>21553</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>138</v>
+        <v>472</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>7</v>
@@ -7130,70 +7233,70 @@
         <v>88</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>219</v>
+        <v>473</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>147</v>
       </c>
       <c r="B148" s="3">
-        <v>21557</v>
+        <v>21556</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>399</v>
+        <v>138</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>400</v>
+        <v>219</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>148</v>
       </c>
       <c r="B149" s="3">
-        <v>21563</v>
+        <v>21557</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>474</v>
+        <v>399</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>475</v>
+        <v>400</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>149</v>
       </c>
       <c r="B150" s="3">
-        <v>21569</v>
+        <v>21563</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>286</v>
+        <v>474</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>7</v>
@@ -7202,22 +7305,22 @@
         <v>88</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>287</v>
+        <v>475</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="B151" s="3">
-        <v>21577</v>
+        <v>21569</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>148</v>
+        <v>286</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>7</v>
@@ -7226,22 +7329,22 @@
         <v>88</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>224</v>
+        <v>287</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>151</v>
       </c>
       <c r="B152" s="3">
-        <v>21579</v>
+        <v>21577</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>333</v>
+        <v>148</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>334</v>
+        <v>107</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>7</v>
@@ -7250,22 +7353,22 @@
         <v>88</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>335</v>
+        <v>224</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>152</v>
       </c>
       <c r="B153" s="3">
-        <v>21581</v>
+        <v>21579</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>147</v>
+        <v>333</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>68</v>
+        <v>334</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>7</v>
@@ -7274,43 +7377,43 @@
         <v>88</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>242</v>
+        <v>335</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>153</v>
       </c>
       <c r="B154" s="3">
-        <v>21584</v>
+        <v>21581</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>397</v>
+        <v>147</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>398</v>
+        <v>242</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>154</v>
       </c>
       <c r="B155" s="3">
-        <v>21587</v>
+        <v>21584</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>20</v>
@@ -7322,19 +7425,19 @@
         <v>88</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>155</v>
       </c>
       <c r="B156" s="3">
-        <v>21588</v>
+        <v>21587</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>20</v>
@@ -7346,67 +7449,67 @@
         <v>88</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>156</v>
       </c>
       <c r="B157" s="3">
-        <v>21593</v>
+        <v>21588</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>273</v>
+        <v>393</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>274</v>
+        <v>394</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>157</v>
       </c>
       <c r="B158" s="3">
-        <v>21604</v>
+        <v>21593</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>318</v>
+        <v>273</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>319</v>
+        <v>274</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>158</v>
       </c>
       <c r="B159" s="3">
-        <v>21607</v>
+        <v>21604</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>401</v>
+        <v>318</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>15</v>
@@ -7418,22 +7521,22 @@
         <v>88</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>402</v>
+        <v>319</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>159</v>
       </c>
       <c r="B160" s="3">
-        <v>21610</v>
+        <v>21607</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>10</v>
@@ -7442,67 +7545,67 @@
         <v>88</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="B161" s="3">
-        <v>21612</v>
+        <v>21610</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>275</v>
+        <v>390</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G161" s="3">
-        <v>21612</v>
+      <c r="G161" s="3" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>161</v>
       </c>
       <c r="B162" s="3">
-        <v>21613</v>
+        <v>21612</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>388</v>
+        <v>275</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G162" s="3" t="s">
-        <v>389</v>
+      <c r="G162" s="3">
+        <v>21612</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>162</v>
       </c>
       <c r="B163" s="3">
-        <v>21614</v>
+        <v>21613</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>20</v>
@@ -7514,19 +7617,19 @@
         <v>88</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>163</v>
       </c>
       <c r="B164" s="3">
-        <v>21615</v>
+        <v>21614</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>20</v>
@@ -7538,19 +7641,19 @@
         <v>88</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>164</v>
       </c>
       <c r="B165" s="3">
-        <v>21616</v>
+        <v>21615</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>20</v>
@@ -7562,22 +7665,22 @@
         <v>88</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>165</v>
       </c>
       <c r="B166" s="3">
-        <v>21619</v>
+        <v>21616</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>464</v>
+        <v>383</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>10</v>
@@ -7586,190 +7689,190 @@
         <v>88</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>465</v>
+        <v>384</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>166</v>
       </c>
       <c r="B167" s="3">
-        <v>21625</v>
+        <v>21619</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>371</v>
+        <v>464</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>372</v>
+        <v>465</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>167</v>
       </c>
       <c r="B168" s="3">
-        <v>21626</v>
+        <v>21625</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G168" s="3">
-        <v>21626</v>
+      <c r="G168" s="3" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>168</v>
       </c>
       <c r="B169" s="3">
-        <v>21630</v>
+        <v>21626</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>369</v>
+        <v>342</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G169" s="3" t="s">
-        <v>370</v>
+      <c r="G169" s="3">
+        <v>21626</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>169</v>
       </c>
       <c r="B170" s="3">
-        <v>21631</v>
+        <v>21630</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>309</v>
+        <v>369</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>310</v>
+        <v>370</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>170</v>
       </c>
       <c r="B171" s="3">
-        <v>21633</v>
+        <v>21631</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G171" s="3">
-        <v>21633</v>
+      <c r="G171" s="3" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>171</v>
       </c>
       <c r="B172" s="3">
-        <v>21634</v>
+        <v>21633</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G172" s="3" t="s">
-        <v>277</v>
+      <c r="G172" s="3">
+        <v>21633</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>172</v>
       </c>
       <c r="B173" s="3">
-        <v>21644</v>
+        <v>21634</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>173</v>
       </c>
       <c r="B174" s="3">
-        <v>21651</v>
+        <v>21644</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>7</v>
@@ -7778,22 +7881,22 @@
         <v>88</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>174</v>
       </c>
       <c r="B175" s="3">
-        <v>21657</v>
+        <v>21651</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>7</v>
@@ -7802,22 +7905,22 @@
         <v>88</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>327</v>
+        <v>251</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>175</v>
       </c>
       <c r="B176" s="3">
-        <v>21661</v>
+        <v>21657</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>7</v>
@@ -7826,142 +7929,142 @@
         <v>88</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>176</v>
       </c>
       <c r="B177" s="3">
-        <v>21663</v>
+        <v>21661</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>343</v>
+        <v>305</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>344</v>
+        <v>306</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>177</v>
       </c>
       <c r="B178" s="3">
-        <v>21665</v>
+        <v>21663</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>292</v>
+        <v>343</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>293</v>
+        <v>344</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>178</v>
       </c>
       <c r="B179" s="3">
-        <v>21666</v>
+        <v>21665</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>179</v>
       </c>
       <c r="B180" s="3">
-        <v>21671</v>
+        <v>21666</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>307</v>
+        <v>278</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>308</v>
+        <v>279</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>180</v>
       </c>
       <c r="B181" s="3">
-        <v>21672</v>
+        <v>21671</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>181</v>
       </c>
       <c r="B182" s="3">
-        <v>21678</v>
+        <v>21672</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>7</v>
@@ -7970,43 +8073,43 @@
         <v>88</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>182</v>
       </c>
       <c r="B183" s="3">
-        <v>21682</v>
+        <v>21678</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>341</v>
+        <v>288</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G183" s="3">
-        <v>21682</v>
+      <c r="G183" s="3" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>183</v>
       </c>
       <c r="B184" s="3">
-        <v>21695</v>
+        <v>21682</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>79</v>
@@ -8018,46 +8121,46 @@
         <v>88</v>
       </c>
       <c r="G184" s="3">
-        <v>21695</v>
+        <v>21682</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>184</v>
       </c>
       <c r="B185" s="3">
-        <v>21698</v>
+        <v>21695</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>303</v>
+        <v>340</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G185" s="3" t="s">
-        <v>304</v>
+      <c r="G185" s="3">
+        <v>21695</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>185</v>
       </c>
       <c r="B186" s="3">
-        <v>21700</v>
+        <v>21698</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>458</v>
+        <v>303</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>7</v>
@@ -8066,19 +8169,19 @@
         <v>88</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>459</v>
+        <v>304</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>186</v>
       </c>
       <c r="B187" s="3">
-        <v>21701</v>
+        <v>21700</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D187" s="3" t="s">
         <v>68</v>
@@ -8090,22 +8193,22 @@
         <v>88</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>187</v>
       </c>
       <c r="B188" s="3">
-        <v>21705</v>
+        <v>21701</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>349</v>
+        <v>456</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>7</v>
@@ -8114,22 +8217,22 @@
         <v>88</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>350</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>188</v>
       </c>
       <c r="B189" s="3">
-        <v>21713</v>
+        <v>21705</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>367</v>
+        <v>35</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>7</v>
@@ -8138,430 +8241,430 @@
         <v>88</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>189</v>
       </c>
       <c r="B190" s="3">
-        <v>21714</v>
+        <v>21710</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>316</v>
+        <v>498</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>317</v>
+        <v>499</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="B191" s="3">
-        <v>21716</v>
+        <v>21713</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>15</v>
+        <v>367</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>191</v>
       </c>
       <c r="B192" s="3">
-        <v>21718</v>
+        <v>21714</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>432</v>
+        <v>316</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>433</v>
+        <v>317</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>192</v>
       </c>
       <c r="B193" s="3">
-        <v>21728</v>
+        <v>21716</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A194:A234" si="3">ROW()-1</f>
         <v>193</v>
       </c>
       <c r="B194" s="3">
-        <v>21736</v>
+        <v>21718</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>322</v>
+        <v>432</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>323</v>
+        <v>433</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>194</v>
       </c>
       <c r="B195" s="3">
-        <v>21748</v>
+        <v>21728</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>195</v>
       </c>
       <c r="B196" s="3">
-        <v>21749</v>
+        <v>21736</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>466</v>
+        <v>322</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>467</v>
+        <v>323</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>196</v>
       </c>
       <c r="B197" s="3">
-        <v>21759</v>
+        <v>21748</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>493</v>
+        <v>351</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>492</v>
+        <v>352</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>197</v>
       </c>
       <c r="B198" s="3">
-        <v>21760</v>
+        <v>21749</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>490</v>
+        <v>466</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>491</v>
+        <v>467</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>198</v>
       </c>
       <c r="B199" s="3">
-        <v>21766</v>
+        <v>21759</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>199</v>
       </c>
       <c r="B200" s="3">
-        <v>21769</v>
+        <v>21760</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>421</v>
+        <v>490</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>422</v>
+        <v>491</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="B201" s="3">
-        <v>21770</v>
+        <v>21766</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>356</v>
+        <v>468</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>357</v>
+        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>201</v>
       </c>
       <c r="B202" s="3">
-        <v>21772</v>
+        <v>21769</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>345</v>
+        <v>421</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>346</v>
+        <v>422</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>202</v>
       </c>
       <c r="B203" s="3">
-        <v>21773</v>
+        <v>21770</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>494</v>
+        <v>356</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>495</v>
+        <v>357</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>203</v>
       </c>
       <c r="B204" s="3">
-        <v>21775</v>
+        <v>21772</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>204</v>
       </c>
       <c r="B205" s="3">
-        <v>21779</v>
+        <v>21773</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>205</v>
       </c>
       <c r="B206" s="3">
-        <v>21782</v>
+        <v>21775</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>446</v>
+        <v>358</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>447</v>
+        <v>359</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>206</v>
       </c>
       <c r="B207" s="3">
-        <v>21783</v>
+        <v>21779</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>7</v>
@@ -8570,43 +8673,43 @@
         <v>88</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>207</v>
       </c>
       <c r="B208" s="3">
-        <v>21784</v>
+        <v>21782</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>379</v>
+        <v>446</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>380</v>
+        <v>447</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>208</v>
       </c>
       <c r="B209" s="3">
-        <v>21787</v>
+        <v>21783</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>427</v>
+        <v>488</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>35</v>
@@ -8618,43 +8721,43 @@
         <v>88</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>428</v>
+        <v>489</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>209</v>
       </c>
       <c r="B210" s="3">
-        <v>21788</v>
+        <v>21784</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>460</v>
+        <v>379</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>461</v>
+        <v>380</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>210</v>
       </c>
       <c r="B211" s="3">
-        <v>21789</v>
+        <v>21787</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>373</v>
+        <v>427</v>
       </c>
       <c r="D211" s="3" t="s">
         <v>35</v>
@@ -8666,46 +8769,46 @@
         <v>88</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>374</v>
+        <v>428</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>211</v>
       </c>
       <c r="B212" s="3">
-        <v>21792</v>
+        <v>21788</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>212</v>
       </c>
       <c r="B213" s="3">
-        <v>21797</v>
+        <v>21789</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>7</v>
@@ -8714,46 +8817,46 @@
         <v>88</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>213</v>
       </c>
       <c r="B214" s="3">
-        <v>21802</v>
+        <v>21792</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>214</v>
       </c>
       <c r="B215" s="3">
-        <v>21807</v>
+        <v>21797</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="E215" s="3" t="s">
         <v>7</v>
@@ -8762,22 +8865,22 @@
         <v>88</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>215</v>
       </c>
       <c r="B216" s="3">
-        <v>21817</v>
+        <v>21802</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E216" s="3" t="s">
         <v>10</v>
@@ -8786,22 +8889,22 @@
         <v>88</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>216</v>
       </c>
       <c r="B217" s="3">
-        <v>21819</v>
+        <v>21807</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>425</v>
+        <v>377</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>367</v>
+        <v>64</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>7</v>
@@ -8810,46 +8913,46 @@
         <v>88</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>426</v>
+        <v>378</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>217</v>
       </c>
       <c r="B218" s="3">
-        <v>21829</v>
+        <v>21817</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>420</v>
+        <v>463</v>
       </c>
     </row>
     <row r="219" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>218</v>
       </c>
       <c r="B219" s="3">
-        <v>21836</v>
+        <v>21819</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>35</v>
+        <v>367</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>7</v>
@@ -8858,43 +8961,43 @@
         <v>88</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
     </row>
     <row r="220" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>219</v>
       </c>
       <c r="B220" s="3">
-        <v>21837</v>
+        <v>21829</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>430</v>
+        <v>35</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
     </row>
     <row r="221" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>220</v>
       </c>
       <c r="B221" s="3">
-        <v>21839</v>
+        <v>21836</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="D221" s="3" t="s">
         <v>35</v>
@@ -8906,19 +9009,19 @@
         <v>88</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>221</v>
       </c>
       <c r="B222" s="3">
-        <v>21840</v>
+        <v>21837</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="D222" s="3" t="s">
         <v>430</v>
@@ -8930,22 +9033,22 @@
         <v>88</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
     </row>
     <row r="223" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>222</v>
       </c>
       <c r="B223" s="3">
-        <v>21850</v>
+        <v>21839</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>7</v>
@@ -8954,171 +9057,291 @@
         <v>88</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="224" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>223</v>
       </c>
       <c r="B224" s="3">
-        <v>21851</v>
+        <v>21840</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>46</v>
+        <v>430</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
     </row>
     <row r="225" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>224</v>
       </c>
       <c r="B225" s="3">
-        <v>21858</v>
+        <v>21847</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>225</v>
       </c>
       <c r="B226" s="3">
-        <v>21863</v>
+        <v>21850</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>471</v>
+        <v>439</v>
       </c>
     </row>
     <row r="227" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>226</v>
       </c>
       <c r="B227" s="3">
-        <v>21864</v>
+        <v>21851</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
     </row>
     <row r="228" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>227</v>
       </c>
       <c r="B228" s="3">
-        <v>21877</v>
+        <v>21858</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="229" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>228</v>
       </c>
       <c r="B229" s="3">
-        <v>21883</v>
+        <v>21863</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
     </row>
     <row r="230" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
+        <f t="shared" si="3"/>
+        <v>229</v>
+      </c>
+      <c r="B230" s="3">
+        <v>21864</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A231" s="3">
+        <f t="shared" si="3"/>
+        <v>230</v>
+      </c>
+      <c r="B231" s="3">
+        <v>21877</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A232" s="3">
+        <f t="shared" si="3"/>
+        <v>231</v>
+      </c>
+      <c r="B232" s="3">
+        <v>21883</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A233" s="3">
+        <f t="shared" si="3"/>
+        <v>232</v>
+      </c>
+      <c r="B233" s="3">
+        <v>21888</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A234" s="3">
+        <f t="shared" si="3"/>
+        <v>233</v>
+      </c>
+      <c r="B234" s="3">
+        <v>21889</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A235" s="3">
         <f>ROW()-1</f>
-        <v>229</v>
-      </c>
-      <c r="B230" s="3"/>
-      <c r="C230" s="3"/>
-      <c r="D230" s="3"/>
-      <c r="E230" s="3"/>
-      <c r="F230" s="3"/>
-      <c r="G230" s="3"/>
+        <v>234</v>
+      </c>
+      <c r="B235" s="3"/>
+      <c r="C235" s="3"/>
+      <c r="D235" s="3"/>
+      <c r="E235" s="3"/>
+      <c r="F235" s="3"/>
+      <c r="G235" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B230">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  <conditionalFormatting sqref="B2:B235">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -9133,14 +9356,17 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="3.77734375" customWidth="1"/>
+    <col min="7" max="7" width="55.77734375" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" customWidth="1"/>
+    <col min="11" max="11" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="55.77734375" customWidth="1"/>
+    <col min="13" max="13" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9184,7 +9410,7 @@
       </c>
       <c r="D2" s="23">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.771929824561403E-3</v>
+        <v>8.5836909871244635E-3</v>
       </c>
       <c r="E2" s="18"/>
       <c r="F2" s="25">
@@ -9196,11 +9422,11 @@
       </c>
       <c r="H2" s="2">
         <f>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>2.6315789473684209E-2</v>
+        <v>3.0042918454935622E-2</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9213,11 +9439,11 @@
       </c>
       <c r="C3" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1929824561403508E-2</v>
+        <v>2.575107296137339E-2</v>
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="25">
@@ -9233,7 +9459,7 @@
       </c>
       <c r="I3" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>8.771929824561403E-3</v>
+        <v>8.5836909871244635E-3</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9250,7 +9476,7 @@
       </c>
       <c r="D4" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>7.0175438596491224E-2</v>
+        <v>6.8669527896995708E-2</v>
       </c>
       <c r="E4" s="18"/>
       <c r="F4" s="25">
@@ -9266,7 +9492,7 @@
       </c>
       <c r="I4" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3157894736842105E-2</v>
+        <v>1.2875536480686695E-2</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9283,7 +9509,7 @@
       </c>
       <c r="D5" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.771929824561403E-3</v>
+        <v>8.5836909871244635E-3</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="25">
@@ -9299,7 +9525,7 @@
       </c>
       <c r="I5" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.19736842105263158</v>
+        <v>0.19313304721030042</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9312,11 +9538,11 @@
       </c>
       <c r="C6" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.7543859649122806E-2</v>
+        <v>2.1459227467811159E-2</v>
       </c>
       <c r="E6" s="18"/>
       <c r="F6" s="25">
@@ -9328,11 +9554,11 @@
       </c>
       <c r="H6" s="2">
         <f>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>1.7543859649122806E-2</v>
+        <v>2.1459227467811159E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9349,7 +9575,7 @@
       </c>
       <c r="D7" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3157894736842105E-2</v>
+        <v>1.2875536480686695E-2</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="7">
@@ -9361,11 +9587,11 @@
       </c>
       <c r="H7" s="8">
         <f>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7" s="19">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.10526315789473684</v>
+        <v>0.1072961373390558</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9382,7 +9608,7 @@
       </c>
       <c r="D8" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.3859649122807015E-3</v>
+        <v>4.2918454935622317E-3</v>
       </c>
       <c r="E8" s="18"/>
       <c r="F8" s="7">
@@ -9394,11 +9620,11 @@
       </c>
       <c r="H8" s="8">
         <f>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</f>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I8" s="19">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.63157894736842102</v>
+        <v>0.62660944206008584</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9415,7 +9641,7 @@
       </c>
       <c r="D9" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.3859649122807015E-3</v>
+        <v>4.2918454935622317E-3</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="26"/>
@@ -9424,7 +9650,7 @@
       </c>
       <c r="H9" s="17">
         <f>SUBTOTAL(109,Table2[عدد الخدمات])</f>
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I9" s="21"/>
     </row>
@@ -9442,7 +9668,7 @@
       </c>
       <c r="D10" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>5.701754385964912E-2</v>
+        <v>5.5793991416309016E-2</v>
       </c>
       <c r="E10" s="18"/>
       <c r="F10" s="25"/>
@@ -9464,7 +9690,7 @@
       </c>
       <c r="D11" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.771929824561403E-3</v>
+        <v>8.5836909871244635E-3</v>
       </c>
       <c r="E11" s="18"/>
       <c r="F11" s="9" t="s">
@@ -9494,7 +9720,7 @@
       </c>
       <c r="D12" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.771929824561403E-3</v>
+        <v>8.5836909871244635E-3</v>
       </c>
       <c r="E12" s="18"/>
       <c r="F12" s="12">
@@ -9509,7 +9735,7 @@
       </c>
       <c r="I12" s="15">
         <f>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</f>
-        <v>7.4561403508771926E-2</v>
+        <v>7.2961373390557943E-2</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.35">
@@ -9526,7 +9752,7 @@
       </c>
       <c r="D13" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3157894736842105E-2</v>
+        <v>1.2875536480686695E-2</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="12">
@@ -9537,11 +9763,11 @@
       </c>
       <c r="H13" s="13">
         <f>COUNTIF(Table1[نوع العمل],Table4[[#This Row],[نوع العمل]])</f>
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="I13" s="15">
         <f>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</f>
-        <v>0.92543859649122806</v>
+        <v>0.92703862660944203</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.35">
@@ -9558,7 +9784,7 @@
       </c>
       <c r="D14" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.771929824561403E-3</v>
+        <v>8.5836909871244635E-3</v>
       </c>
       <c r="E14" s="18"/>
       <c r="F14" s="12"/>
@@ -9567,7 +9793,7 @@
       </c>
       <c r="H14" s="13">
         <f>SUBTOTAL(109,Table4[عدد الخدمات])</f>
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I14" s="14"/>
     </row>
@@ -9585,7 +9811,7 @@
       </c>
       <c r="D15" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.3859649122807015E-3</v>
+        <v>4.2918454935622317E-3</v>
       </c>
       <c r="E15" s="18"/>
     </row>
@@ -9603,11 +9829,23 @@
       </c>
       <c r="D16" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>7.0175438596491224E-2</v>
+        <v>6.8669527896995708E-2</v>
       </c>
       <c r="E16" s="18"/>
-    </row>
-    <row r="17" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="F16" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" s="31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -9621,11 +9859,26 @@
       </c>
       <c r="D17" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.3859649122807015E-3</v>
+        <v>4.2918454935622317E-3</v>
       </c>
       <c r="E17" s="18"/>
-    </row>
-    <row r="18" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="F17" s="29">
+        <f>ROW()-16</f>
+        <v>1</v>
+      </c>
+      <c r="G17" s="30" t="str" cm="1">
+        <f t="array" ref="G17:H19">_xlfn.TAKE(_xlfn.SORTBY(Table3[[اسم الجهة]:[عدد الخدمات]],Table3[عدد الخدمات],-1),3)</f>
+        <v>وزارة التربية والتعليم</v>
+      </c>
+      <c r="H17" s="30">
+        <v>25</v>
+      </c>
+      <c r="I17" s="32">
+        <f>H17/SUM(Table3[عدد الخدمات])</f>
+        <v>0.1072961373390558</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -9639,11 +9892,25 @@
       </c>
       <c r="D18" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3157894736842105E-2</v>
+        <v>1.2875536480686695E-2</v>
       </c>
       <c r="E18" s="18"/>
-    </row>
-    <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="F18" s="29">
+        <f>ROW()-16</f>
+        <v>2</v>
+      </c>
+      <c r="G18" s="2" t="str">
+        <v>وزارة الهجرة والمهجرين</v>
+      </c>
+      <c r="H18" s="2">
+        <v>23</v>
+      </c>
+      <c r="I18" s="16">
+        <f>H18/SUM(Table3[عدد الخدمات])</f>
+        <v>9.8712446351931327E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -9653,15 +9920,29 @@
       </c>
       <c r="C19" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.7543859649122806E-2</v>
+        <v>2.1459227467811159E-2</v>
       </c>
       <c r="E19" s="18"/>
-    </row>
-    <row r="20" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="F19" s="29">
+        <f>ROW()-16</f>
+        <v>3</v>
+      </c>
+      <c r="G19" s="30" t="str">
+        <v>الهيئة الوطنية للرقابة النووية والاشعاعية والكيميائية والبايولوجية</v>
+      </c>
+      <c r="H19" s="30">
+        <v>16</v>
+      </c>
+      <c r="I19" s="32">
+        <f>H19/SUM(Table3[عدد الخدمات])</f>
+        <v>6.8669527896995708E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -9675,11 +9956,20 @@
       </c>
       <c r="D20" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.3859649122807015E-3</v>
+        <v>4.2918454935622317E-3</v>
       </c>
       <c r="E20" s="18"/>
-    </row>
-    <row r="21" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="F20" s="33"/>
+      <c r="G20" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="34">
+        <f>SUM(H17:H19)</f>
+        <v>64</v>
+      </c>
+      <c r="I20" s="35"/>
+    </row>
+    <row r="21" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -9693,11 +9983,11 @@
       </c>
       <c r="D21" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.771929824561403E-3</v>
+        <v>8.5836909871244635E-3</v>
       </c>
       <c r="E21" s="18"/>
     </row>
-    <row r="22" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -9711,11 +10001,23 @@
       </c>
       <c r="D22" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.3859649122807015E-3</v>
+        <v>4.2918454935622317E-3</v>
       </c>
       <c r="E22" s="18"/>
-    </row>
-    <row r="23" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="F22" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -9729,11 +10031,26 @@
       </c>
       <c r="D23" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.0701754385964911E-2</v>
+        <v>3.0042918454935622E-2</v>
       </c>
       <c r="E23" s="18"/>
-    </row>
-    <row r="24" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="F23" s="29">
+        <f>ROW()-21</f>
+        <v>2</v>
+      </c>
+      <c r="G23" s="30" t="str" cm="1">
+        <f t="array" ref="G23:H25">_xlfn.TAKE(_xlfn.SORTBY(Table3[[اسم الجهة]:[عدد الخدمات]],Table3[عدد الخدمات],1),3)</f>
+        <v>محافظة الانبار</v>
+      </c>
+      <c r="H23" s="30">
+        <v>1</v>
+      </c>
+      <c r="I23" s="32">
+        <f>H23/SUM(Table3[عدد الخدمات])</f>
+        <v>4.2918454935622317E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -9747,11 +10064,25 @@
       </c>
       <c r="D24" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.6315789473684209E-2</v>
+        <v>2.575107296137339E-2</v>
       </c>
       <c r="E24" s="18"/>
-    </row>
-    <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="F24" s="29">
+        <f>ROW()-21</f>
+        <v>3</v>
+      </c>
+      <c r="G24" s="2" t="str">
+        <v>محافظة البصرة</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="16">
+        <f>H24/SUM(Table3[عدد الخدمات])</f>
+        <v>4.2918454935622317E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -9761,15 +10092,29 @@
       </c>
       <c r="C25" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.5087719298245612E-2</v>
+        <v>3.8626609442060089E-2</v>
       </c>
       <c r="E25" s="18"/>
-    </row>
-    <row r="26" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="F25" s="29">
+        <f>ROW()-21</f>
+        <v>4</v>
+      </c>
+      <c r="G25" s="30" t="str">
+        <v>محافظة صلاح الدين</v>
+      </c>
+      <c r="H25" s="30">
+        <v>1</v>
+      </c>
+      <c r="I25" s="32">
+        <f>H25/SUM(Table3[عدد الخدمات])</f>
+        <v>4.2918454935622317E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -9783,11 +10128,20 @@
       </c>
       <c r="D26" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>0.10964912280701754</v>
+        <v>0.1072961373390558</v>
       </c>
       <c r="E26" s="18"/>
-    </row>
-    <row r="27" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="F26" s="33"/>
+      <c r="G26" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="34">
+        <f>SUM(H23:H25)</f>
+        <v>3</v>
+      </c>
+      <c r="I26" s="35"/>
+    </row>
+    <row r="27" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -9801,11 +10155,11 @@
       </c>
       <c r="D27" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.3859649122807015E-3</v>
+        <v>4.2918454935622317E-3</v>
       </c>
       <c r="E27" s="18"/>
     </row>
-    <row r="28" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -9819,11 +10173,11 @@
       </c>
       <c r="D28" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.9473684210526314E-2</v>
+        <v>3.8626609442060089E-2</v>
       </c>
       <c r="E28" s="18"/>
     </row>
-    <row r="29" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -9837,10 +10191,10 @@
       </c>
       <c r="D29" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1929824561403508E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+        <v>2.1459227467811159E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -9850,14 +10204,14 @@
       </c>
       <c r="C30" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1929824561403508E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+        <v>2.575107296137339E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -9871,10 +10225,10 @@
       </c>
       <c r="D31" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.7543859649122806E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+        <v>1.7167381974248927E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -9888,7 +10242,7 @@
       </c>
       <c r="D32" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1929824561403508E-2</v>
+        <v>2.1459227467811159E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9905,7 +10259,7 @@
       </c>
       <c r="D33" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3157894736842105E-2</v>
+        <v>1.2875536480686695E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9922,7 +10276,7 @@
       </c>
       <c r="D34" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.3859649122807015E-2</v>
+        <v>4.2918454935622317E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9939,7 +10293,7 @@
       </c>
       <c r="D35" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.771929824561403E-3</v>
+        <v>8.5836909871244635E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9956,7 +10310,7 @@
       </c>
       <c r="D36" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.3859649122807015E-3</v>
+        <v>4.2918454935622317E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9973,7 +10327,7 @@
       </c>
       <c r="D37" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.9473684210526314E-2</v>
+        <v>3.8626609442060089E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9990,7 +10344,7 @@
       </c>
       <c r="D38" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.9473684210526314E-2</v>
+        <v>3.8626609442060089E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10007,7 +10361,7 @@
       </c>
       <c r="D39" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.3859649122807015E-2</v>
+        <v>4.2918454935622317E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10024,7 +10378,7 @@
       </c>
       <c r="D40" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.3859649122807015E-3</v>
+        <v>4.2918454935622317E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10041,7 +10395,7 @@
       </c>
       <c r="D41" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>0.10087719298245613</v>
+        <v>9.8712446351931327E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10051,11 +10405,11 @@
       </c>
       <c r="C42" s="8">
         <f>SUBTOTAL(109,Table3[عدد الخدمات])</f>
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D42" s="20">
         <f>SUBTOTAL(109,Table3[النسبة المئوية])</f>
-        <v>1.0000000000000002</v>
+        <v>0.99999999999999978</v>
       </c>
     </row>
   </sheetData>

--- a/الخدمات.xlsx
+++ b/الخدمات.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a843af4fc71c607/Desktop/JavaScript codes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3295" documentId="11_6D1415C555E27CE26E339E56ADDC14C75C28AAF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1000008D-9CCA-4D56-824E-B608BFB5304F}"/>
+  <xr:revisionPtr revIDLastSave="3320" documentId="11_6D1415C555E27CE26E339E56ADDC14C75C28AAF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F48E0C5D-6B17-43B2-872E-F98BA3498AE0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="512">
   <si>
     <t>ت.</t>
   </si>
@@ -1577,6 +1577,24 @@
   </si>
   <si>
     <t>تقديم على اعتراض</t>
+  </si>
+  <si>
+    <t>التقديم الالكتروني على معاهد التدريب النفطي للعام الدراسي (2026-2027)</t>
+  </si>
+  <si>
+    <t>معاهد التدريب النفطي 2</t>
+  </si>
+  <si>
+    <t>شكاوي واستفسارات الخاص بالاكاديمية العسكرية - وزارة الدفاع</t>
+  </si>
+  <si>
+    <t>اكاديمية عسكرية</t>
+  </si>
+  <si>
+    <t>استبانة رضا الاطراف المعنية</t>
+  </si>
+  <si>
+    <t>رضا اطراف معنية</t>
   </si>
 </sst>
 </file>
@@ -1914,7 +1932,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="57">
+  <dxfs count="58">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3355,39 +3383,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G235" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G238" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G234">
     <sortCondition ref="B2:B234"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{20FD99FD-87DB-4DD1-989A-014AAE8F25F6}" name="ت." dataDxfId="53" totalsRowDxfId="52">
+    <tableColumn id="1" xr3:uid="{20FD99FD-87DB-4DD1-989A-014AAE8F25F6}" name="ت." dataDxfId="54" totalsRowDxfId="53">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F323E4AC-F323-4F97-9904-326D9949B165}" name="رقم الخدمة" dataDxfId="51" totalsRowDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{58A3CC8C-66BF-4DA6-B0EF-C7F43089C5C0}" name="اسم الخدمة" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{176DB514-0824-46BC-9146-CAA89D7A742F}" name="جهة الخدمة" dataDxfId="47" totalsRowDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{E4173C63-A839-4611-8E53-7B3AE2F439DB}" name="نوع الجهة" dataDxfId="45" totalsRowDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{C01A4E12-3E16-4DE9-86B3-69F70894487E}" name="نوع العمل" dataDxfId="43" totalsRowDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{3481871F-BF9F-4C45-AC54-67A9AF362483}" name="اسم الملف" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{F323E4AC-F323-4F97-9904-326D9949B165}" name="رقم الخدمة" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{58A3CC8C-66BF-4DA6-B0EF-C7F43089C5C0}" name="اسم الخدمة" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{176DB514-0824-46BC-9146-CAA89D7A742F}" name="جهة الخدمة" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{E4173C63-A839-4611-8E53-7B3AE2F439DB}" name="نوع الجهة" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{C01A4E12-3E16-4DE9-86B3-69F70894487E}" name="نوع العمل" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{3481871F-BF9F-4C45-AC54-67A9AF362483}" name="اسم الملف" dataDxfId="42" totalsRowDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="39" dataDxfId="37" totalsRowDxfId="36" headerRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="40" dataDxfId="38" totalsRowDxfId="37" headerRowBorderDxfId="39">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F2:I8">
     <sortCondition ref="G2:G8"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FDC31943-D832-4BCF-8A6F-51F74847839D}" name="ت." dataDxfId="35" totalsRowDxfId="34">
+    <tableColumn id="1" xr3:uid="{FDC31943-D832-4BCF-8A6F-51F74847839D}" name="ت." dataDxfId="36" totalsRowDxfId="35">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D6F61CFE-6FB5-4088-802C-280AB03DDC3F}" name="نوع الجهة" totalsRowLabel="المجموع" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{819F64F0-7B30-437C-8552-96E1BA009158}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="2" xr3:uid="{D6F61CFE-6FB5-4088-802C-280AB03DDC3F}" name="نوع الجهة" totalsRowLabel="المجموع" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{819F64F0-7B30-437C-8552-96E1BA009158}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
       <calculatedColumnFormula>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D928E8D0-BE48-4700-B3FA-A3A0C6ED8D95}" name="النسبة المئوية" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{D928E8D0-BE48-4700-B3FA-A3A0C6ED8D95}" name="النسبة المئوية" dataDxfId="30" totalsRowDxfId="29" dataCellStyle="Percent">
       <calculatedColumnFormula>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3396,19 +3424,19 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D42" totalsRowCount="1" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D42" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D41">
     <sortCondition ref="B2:B41"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{04CB5523-1DF6-4CA0-AC24-1D21F85D9F94}" name="ت." dataDxfId="22" totalsRowDxfId="21">
+    <tableColumn id="1" xr3:uid="{04CB5523-1DF6-4CA0-AC24-1D21F85D9F94}" name="ت." dataDxfId="23" totalsRowDxfId="22">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{966ACB29-C086-4C8E-BD62-D0F9ECCCA301}" name="اسم الجهة" totalsRowLabel="المجموع" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{E47A3AE0-B7A7-44F8-8FA6-8FA757A3066F}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="17">
+    <tableColumn id="2" xr3:uid="{966ACB29-C086-4C8E-BD62-D0F9ECCCA301}" name="اسم الجهة" totalsRowLabel="المجموع" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{E47A3AE0-B7A7-44F8-8FA6-8FA757A3066F}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18">
       <calculatedColumnFormula>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0D34DEDD-061D-44F4-9DA6-86D41E4BDDB7}" name="النسبة المئوية" totalsRowFunction="sum" dataDxfId="16" totalsRowDxfId="15" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{0D34DEDD-061D-44F4-9DA6-86D41E4BDDB7}" name="النسبة المئوية" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Percent">
       <calculatedColumnFormula>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3417,16 +3445,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="9" totalsRowDxfId="8">
+    <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="10" totalsRowDxfId="9">
       <calculatedColumnFormula>ROW()-11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4A8E3EC9-46C6-46A2-85BB-E7D02B7ABF90}" name="نوع العمل" totalsRowLabel="المجموع" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{140AD779-6235-4A33-848F-7CF18BA55E33}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4">
+    <tableColumn id="2" xr3:uid="{4A8E3EC9-46C6-46A2-85BB-E7D02B7ABF90}" name="نوع العمل" totalsRowLabel="المجموع" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{140AD779-6235-4A33-848F-7CF18BA55E33}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="5">
       <calculatedColumnFormula>COUNTIF(Table1[نوع العمل],Table4[[#This Row],[نوع العمل]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CD921388-F9B8-4CDD-A07C-FBB8C0ABF589}" name="النسبة المئوية" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Percent">
+    <tableColumn id="4" xr3:uid="{CD921388-F9B8-4CDD-A07C-FBB8C0ABF589}" name="النسبة المئوية" dataDxfId="4" totalsRowDxfId="3" dataCellStyle="Percent">
       <calculatedColumnFormula>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3697,7 +3725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G235"/>
+  <dimension ref="A1:G238"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
@@ -9329,19 +9357,91 @@
         <f>ROW()-1</f>
         <v>234</v>
       </c>
-      <c r="B235" s="3"/>
-      <c r="C235" s="3"/>
-      <c r="D235" s="3"/>
-      <c r="E235" s="3"/>
-      <c r="F235" s="3"/>
-      <c r="G235" s="3"/>
+      <c r="B235" s="3">
+        <v>21916</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A236" s="3">
+        <f>ROW()-1</f>
+        <v>235</v>
+      </c>
+      <c r="B236" s="3">
+        <v>21799</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A237" s="3">
+        <f>ROW()-1</f>
+        <v>236</v>
+      </c>
+      <c r="B237" s="3">
+        <v>21898</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A238" s="3">
+        <f>ROW()-1</f>
+        <v>237</v>
+      </c>
+      <c r="B238" s="3"/>
+      <c r="C238" s="3"/>
+      <c r="D238" s="3"/>
+      <c r="E238" s="3"/>
+      <c r="F238" s="3"/>
+      <c r="G238" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B235">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="B2:B238">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -9410,7 +9510,7 @@
       </c>
       <c r="D2" s="23">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.5836909871244635E-3</v>
+        <v>8.4745762711864406E-3</v>
       </c>
       <c r="E2" s="18"/>
       <c r="F2" s="25">
@@ -9426,7 +9526,7 @@
       </c>
       <c r="I2" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>3.0042918454935622E-2</v>
+        <v>2.9661016949152543E-2</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9443,7 +9543,7 @@
       </c>
       <c r="D3" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.575107296137339E-2</v>
+        <v>2.5423728813559324E-2</v>
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="25">
@@ -9459,7 +9559,7 @@
       </c>
       <c r="I3" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>8.5836909871244635E-3</v>
+        <v>8.4745762711864406E-3</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9476,7 +9576,7 @@
       </c>
       <c r="D4" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>6.8669527896995708E-2</v>
+        <v>6.7796610169491525E-2</v>
       </c>
       <c r="E4" s="18"/>
       <c r="F4" s="25">
@@ -9492,7 +9592,7 @@
       </c>
       <c r="I4" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2875536480686695E-2</v>
+        <v>1.2711864406779662E-2</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9509,7 +9609,7 @@
       </c>
       <c r="D5" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.5836909871244635E-3</v>
+        <v>8.4745762711864406E-3</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="25">
@@ -9525,7 +9625,7 @@
       </c>
       <c r="I5" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.19313304721030042</v>
+        <v>0.19067796610169491</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9542,7 +9642,7 @@
       </c>
       <c r="D6" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1459227467811159E-2</v>
+        <v>2.1186440677966101E-2</v>
       </c>
       <c r="E6" s="18"/>
       <c r="F6" s="25">
@@ -9558,7 +9658,7 @@
       </c>
       <c r="I6" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1459227467811159E-2</v>
+        <v>2.1186440677966101E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9575,7 +9675,7 @@
       </c>
       <c r="D7" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2875536480686695E-2</v>
+        <v>1.2711864406779662E-2</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="7">
@@ -9591,7 +9691,7 @@
       </c>
       <c r="I7" s="19">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.1072961373390558</v>
+        <v>0.1059322033898305</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9608,7 +9708,7 @@
       </c>
       <c r="D8" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2918454935622317E-3</v>
+        <v>4.2372881355932203E-3</v>
       </c>
       <c r="E8" s="18"/>
       <c r="F8" s="7">
@@ -9620,11 +9720,11 @@
       </c>
       <c r="H8" s="8">
         <f>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</f>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I8" s="19">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.62660944206008584</v>
+        <v>0.63135593220338981</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9641,7 +9741,7 @@
       </c>
       <c r="D9" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2918454935622317E-3</v>
+        <v>4.2372881355932203E-3</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="26"/>
@@ -9650,7 +9750,7 @@
       </c>
       <c r="H9" s="17">
         <f>SUBTOTAL(109,Table2[عدد الخدمات])</f>
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I9" s="21"/>
     </row>
@@ -9668,7 +9768,7 @@
       </c>
       <c r="D10" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>5.5793991416309016E-2</v>
+        <v>5.5084745762711863E-2</v>
       </c>
       <c r="E10" s="18"/>
       <c r="F10" s="25"/>
@@ -9690,7 +9790,7 @@
       </c>
       <c r="D11" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.5836909871244635E-3</v>
+        <v>8.4745762711864406E-3</v>
       </c>
       <c r="E11" s="18"/>
       <c r="F11" s="9" t="s">
@@ -9720,7 +9820,7 @@
       </c>
       <c r="D12" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.5836909871244635E-3</v>
+        <v>8.4745762711864406E-3</v>
       </c>
       <c r="E12" s="18"/>
       <c r="F12" s="12">
@@ -9735,7 +9835,7 @@
       </c>
       <c r="I12" s="15">
         <f>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</f>
-        <v>7.2961373390557943E-2</v>
+        <v>7.2033898305084748E-2</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.35">
@@ -9752,7 +9852,7 @@
       </c>
       <c r="D13" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2875536480686695E-2</v>
+        <v>1.2711864406779662E-2</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="12">
@@ -9763,11 +9863,11 @@
       </c>
       <c r="H13" s="13">
         <f>COUNTIF(Table1[نوع العمل],Table4[[#This Row],[نوع العمل]])</f>
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I13" s="15">
         <f>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</f>
-        <v>0.92703862660944203</v>
+        <v>0.92796610169491522</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.35">
@@ -9784,7 +9884,7 @@
       </c>
       <c r="D14" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.5836909871244635E-3</v>
+        <v>8.4745762711864406E-3</v>
       </c>
       <c r="E14" s="18"/>
       <c r="F14" s="12"/>
@@ -9793,7 +9893,7 @@
       </c>
       <c r="H14" s="13">
         <f>SUBTOTAL(109,Table4[عدد الخدمات])</f>
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I14" s="14"/>
     </row>
@@ -9811,7 +9911,7 @@
       </c>
       <c r="D15" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2918454935622317E-3</v>
+        <v>4.2372881355932203E-3</v>
       </c>
       <c r="E15" s="18"/>
     </row>
@@ -9829,7 +9929,7 @@
       </c>
       <c r="D16" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>6.8669527896995708E-2</v>
+        <v>6.7796610169491525E-2</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="27" t="s">
@@ -9859,7 +9959,7 @@
       </c>
       <c r="D17" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2918454935622317E-3</v>
+        <v>4.2372881355932203E-3</v>
       </c>
       <c r="E17" s="18"/>
       <c r="F17" s="29">
@@ -9875,7 +9975,7 @@
       </c>
       <c r="I17" s="32">
         <f>H17/SUM(Table3[عدد الخدمات])</f>
-        <v>0.1072961373390558</v>
+        <v>0.1059322033898305</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9892,7 +9992,7 @@
       </c>
       <c r="D18" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2875536480686695E-2</v>
+        <v>1.2711864406779662E-2</v>
       </c>
       <c r="E18" s="18"/>
       <c r="F18" s="29">
@@ -9907,7 +10007,7 @@
       </c>
       <c r="I18" s="16">
         <f>H18/SUM(Table3[عدد الخدمات])</f>
-        <v>9.8712446351931327E-2</v>
+        <v>9.7457627118644072E-2</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9924,7 +10024,7 @@
       </c>
       <c r="D19" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1459227467811159E-2</v>
+        <v>2.1186440677966101E-2</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="29">
@@ -9939,7 +10039,7 @@
       </c>
       <c r="I19" s="32">
         <f>H19/SUM(Table3[عدد الخدمات])</f>
-        <v>6.8669527896995708E-2</v>
+        <v>6.7796610169491525E-2</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9956,7 +10056,7 @@
       </c>
       <c r="D20" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2918454935622317E-3</v>
+        <v>4.2372881355932203E-3</v>
       </c>
       <c r="E20" s="18"/>
       <c r="F20" s="33"/>
@@ -9983,7 +10083,7 @@
       </c>
       <c r="D21" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.5836909871244635E-3</v>
+        <v>8.4745762711864406E-3</v>
       </c>
       <c r="E21" s="18"/>
     </row>
@@ -9997,11 +10097,11 @@
       </c>
       <c r="C22" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2918454935622317E-3</v>
+        <v>8.4745762711864406E-3</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="27" t="s">
@@ -10031,7 +10131,7 @@
       </c>
       <c r="D23" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.0042918454935622E-2</v>
+        <v>2.9661016949152543E-2</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="29">
@@ -10047,7 +10147,7 @@
       </c>
       <c r="I23" s="32">
         <f>H23/SUM(Table3[عدد الخدمات])</f>
-        <v>4.2918454935622317E-3</v>
+        <v>4.2372881355932203E-3</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10064,7 +10164,7 @@
       </c>
       <c r="D24" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.575107296137339E-2</v>
+        <v>2.5423728813559324E-2</v>
       </c>
       <c r="E24" s="18"/>
       <c r="F24" s="29">
@@ -10079,7 +10179,7 @@
       </c>
       <c r="I24" s="16">
         <f>H24/SUM(Table3[عدد الخدمات])</f>
-        <v>4.2918454935622317E-3</v>
+        <v>4.2372881355932203E-3</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10096,7 +10196,7 @@
       </c>
       <c r="D25" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.8626609442060089E-2</v>
+        <v>3.8135593220338986E-2</v>
       </c>
       <c r="E25" s="18"/>
       <c r="F25" s="29">
@@ -10111,7 +10211,7 @@
       </c>
       <c r="I25" s="32">
         <f>H25/SUM(Table3[عدد الخدمات])</f>
-        <v>4.2918454935622317E-3</v>
+        <v>4.2372881355932203E-3</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10128,7 +10228,7 @@
       </c>
       <c r="D26" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>0.1072961373390558</v>
+        <v>0.1059322033898305</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="33"/>
@@ -10155,7 +10255,7 @@
       </c>
       <c r="D27" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2918454935622317E-3</v>
+        <v>4.2372881355932203E-3</v>
       </c>
       <c r="E27" s="18"/>
     </row>
@@ -10173,7 +10273,7 @@
       </c>
       <c r="D28" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.8626609442060089E-2</v>
+        <v>3.8135593220338986E-2</v>
       </c>
       <c r="E28" s="18"/>
     </row>
@@ -10191,7 +10291,7 @@
       </c>
       <c r="D29" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1459227467811159E-2</v>
+        <v>2.1186440677966101E-2</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10204,11 +10304,11 @@
       </c>
       <c r="C30" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.575107296137339E-2</v>
+        <v>2.9661016949152543E-2</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10225,7 +10325,7 @@
       </c>
       <c r="D31" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.7167381974248927E-2</v>
+        <v>1.6949152542372881E-2</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10242,7 +10342,7 @@
       </c>
       <c r="D32" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1459227467811159E-2</v>
+        <v>2.1186440677966101E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10259,7 +10359,7 @@
       </c>
       <c r="D33" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2875536480686695E-2</v>
+        <v>1.2711864406779662E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10276,7 +10376,7 @@
       </c>
       <c r="D34" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2918454935622317E-2</v>
+        <v>4.2372881355932202E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10293,7 +10393,7 @@
       </c>
       <c r="D35" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.5836909871244635E-3</v>
+        <v>8.4745762711864406E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10310,7 +10410,7 @@
       </c>
       <c r="D36" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2918454935622317E-3</v>
+        <v>4.2372881355932203E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10327,7 +10427,7 @@
       </c>
       <c r="D37" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.8626609442060089E-2</v>
+        <v>3.8135593220338986E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10344,7 +10444,7 @@
       </c>
       <c r="D38" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.8626609442060089E-2</v>
+        <v>3.8135593220338986E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10357,11 +10457,11 @@
       </c>
       <c r="C39" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D39" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2918454935622317E-2</v>
+        <v>4.6610169491525424E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10378,7 +10478,7 @@
       </c>
       <c r="D40" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2918454935622317E-3</v>
+        <v>4.2372881355932203E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10395,7 +10495,7 @@
       </c>
       <c r="D41" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.8712446351931327E-2</v>
+        <v>9.7457627118644072E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10405,7 +10505,7 @@
       </c>
       <c r="C42" s="8">
         <f>SUBTOTAL(109,Table3[عدد الخدمات])</f>
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D42" s="20">
         <f>SUBTOTAL(109,Table3[النسبة المئوية])</f>

--- a/الخدمات.xlsx
+++ b/الخدمات.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a843af4fc71c607/Desktop/JavaScript codes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3320" documentId="11_6D1415C555E27CE26E339E56ADDC14C75C28AAF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F48E0C5D-6B17-43B2-872E-F98BA3498AE0}"/>
+  <xr:revisionPtr revIDLastSave="3447" documentId="11_6D1415C555E27CE26E339E56ADDC14C75C28AAF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A91B43B-50A1-436F-9000-D22321047410}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="معلومات الخدمات" sheetId="1" r:id="rId1"/>
-    <sheet name="احصائيات" sheetId="2" r:id="rId2"/>
+    <sheet name="الدفع الالكتروني" sheetId="3" r:id="rId2"/>
+    <sheet name="احصائيات" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="525">
   <si>
     <t>ت.</t>
   </si>
@@ -1595,6 +1596,45 @@
   </si>
   <si>
     <t>رضا اطراف معنية</t>
+  </si>
+  <si>
+    <t>استيفاء اجور الخدمات المقدمة من دائرة المعهد العالي لأعداد وتأهيل القادة</t>
+  </si>
+  <si>
+    <t>الأمانة العامة لمجلس الوزراء</t>
+  </si>
+  <si>
+    <t>مستقلة</t>
+  </si>
+  <si>
+    <t>استيفاء أجور</t>
+  </si>
+  <si>
+    <t>مكان الدفع</t>
+  </si>
+  <si>
+    <t>الاستمارة</t>
+  </si>
+  <si>
+    <t>تقديم طلب الكتروني لغرض الشمول بالتأمين الهندسي لدى شركة التأمين العراقية</t>
+  </si>
+  <si>
+    <t>التامين الهندسي</t>
+  </si>
+  <si>
+    <t>المحطة</t>
+  </si>
+  <si>
+    <t>تقديم طلب إلكتروني للتأمين من الحوادث الشخصية وحوادث الارهاب لدى شركة التأمين العراقية</t>
+  </si>
+  <si>
+    <t>شخصية وإرهاب</t>
+  </si>
+  <si>
+    <t>طلب وثيقة تخرج</t>
+  </si>
+  <si>
+    <t>وثيقة تخرج</t>
   </si>
 </sst>
 </file>
@@ -1822,7 +1862,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1927,12 +1967,24 @@
     <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="58">
+  <dxfs count="71">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3365,6 +3417,296 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3383,7 +3725,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G238" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G239" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G234">
     <sortCondition ref="B2:B234"/>
   </sortState>
@@ -3403,6 +3745,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{84F97999-FBC9-427B-AC68-DAFBADA61BB8}" name="Table5" displayName="Table5" ref="A1:H6" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67" totalsRowBorderDxfId="66">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{69E53D5C-73E1-4C2D-A2FF-8B09CE7A5D9B}" name="ت." dataDxfId="65">
+      <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{EBAAD0E3-6F6D-4DE2-A8C7-BC5A0EEE6FE2}" name="رقم الخدمة" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{0BCF7553-361D-472A-8D6B-445844D28E52}" name="اسم الخدمة" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{3E2F9AA3-02D8-4C6F-8CBA-BA47686A8C20}" name="جهة الخدمة" dataDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{9F37D9B7-7A9A-4709-8DFC-E6579BBF5270}" name="نوع الجهة" dataDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{2DD6D84B-0F1F-4F7E-BFC9-49CC99A8B055}" name="نوع العمل" dataDxfId="60"/>
+    <tableColumn id="10" xr3:uid="{97CE7C95-A47D-44C9-B115-777267316E94}" name="اسم الملف" dataDxfId="59"/>
+    <tableColumn id="7" xr3:uid="{2C0E9C57-3204-4A1B-B24D-2DE53DDD9D13}" name="مكان الدفع" dataDxfId="58"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="40" dataDxfId="38" totalsRowDxfId="37" headerRowBorderDxfId="39">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F2:I8">
     <sortCondition ref="G2:G8"/>
@@ -3423,7 +3783,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D42" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D41">
     <sortCondition ref="B2:B41"/>
@@ -3444,7 +3804,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="10" totalsRowDxfId="9">
@@ -3725,7 +4085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G238"/>
+  <dimension ref="A1:G239"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
@@ -9429,18 +9789,42 @@
         <f>ROW()-1</f>
         <v>237</v>
       </c>
-      <c r="B238" s="3"/>
-      <c r="C238" s="3"/>
-      <c r="D238" s="3"/>
-      <c r="E238" s="3"/>
-      <c r="F238" s="3"/>
-      <c r="G238" s="3"/>
+      <c r="B238" s="3">
+        <v>21880</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A239" s="3">
+        <f>ROW()-1</f>
+        <v>238</v>
+      </c>
+      <c r="B239" s="3"/>
+      <c r="C239" s="3"/>
+      <c r="D239" s="3"/>
+      <c r="E239" s="3"/>
+      <c r="F239" s="3"/>
+      <c r="G239" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B238">
+  <conditionalFormatting sqref="B2:B239">
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9451,6 +9835,176 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{611420FC-D4C7-424A-870C-F1AC7FD39257}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="38">
+        <f>ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
+        <v>21911</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>515</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A3" s="38">
+        <f>ROW()-1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
+        <v>10617</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="39" t="s">
+        <v>519</v>
+      </c>
+      <c r="H3" s="39" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="38">
+        <f>ROW()-1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>21293</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="39" t="s">
+        <v>522</v>
+      </c>
+      <c r="H4" s="39" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A5" s="38">
+        <f>ROW()-1</f>
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>21766</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="39" t="s">
+        <v>467</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A6" s="38">
+        <f>ROW()-1</f>
+        <v>5</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5F6050-FB7D-4193-8E9E-199F19695B01}">
   <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9510,7 +10064,7 @@
       </c>
       <c r="D2" s="23">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4745762711864406E-3</v>
+        <v>8.4388185654008432E-3</v>
       </c>
       <c r="E2" s="18"/>
       <c r="F2" s="25">
@@ -9526,7 +10080,7 @@
       </c>
       <c r="I2" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>2.9661016949152543E-2</v>
+        <v>2.9535864978902954E-2</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9543,7 +10097,7 @@
       </c>
       <c r="D3" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.5423728813559324E-2</v>
+        <v>2.5316455696202531E-2</v>
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="25">
@@ -9559,7 +10113,7 @@
       </c>
       <c r="I3" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4745762711864406E-3</v>
+        <v>8.4388185654008432E-3</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9576,7 +10130,7 @@
       </c>
       <c r="D4" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>6.7796610169491525E-2</v>
+        <v>6.7510548523206745E-2</v>
       </c>
       <c r="E4" s="18"/>
       <c r="F4" s="25">
@@ -9592,7 +10146,7 @@
       </c>
       <c r="I4" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2711864406779662E-2</v>
+        <v>1.2658227848101266E-2</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9609,7 +10163,7 @@
       </c>
       <c r="D5" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4745762711864406E-3</v>
+        <v>8.4388185654008432E-3</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="25">
@@ -9625,7 +10179,7 @@
       </c>
       <c r="I5" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.19067796610169491</v>
+        <v>0.189873417721519</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9642,7 +10196,7 @@
       </c>
       <c r="D6" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1186440677966101E-2</v>
+        <v>2.1097046413502109E-2</v>
       </c>
       <c r="E6" s="18"/>
       <c r="F6" s="25">
@@ -9658,7 +10212,7 @@
       </c>
       <c r="I6" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1186440677966101E-2</v>
+        <v>2.1097046413502109E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9675,7 +10229,7 @@
       </c>
       <c r="D7" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2711864406779662E-2</v>
+        <v>1.2658227848101266E-2</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="7">
@@ -9691,7 +10245,7 @@
       </c>
       <c r="I7" s="19">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.1059322033898305</v>
+        <v>0.10548523206751055</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9708,7 +10262,7 @@
       </c>
       <c r="D8" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2372881355932203E-3</v>
+        <v>4.2194092827004216E-3</v>
       </c>
       <c r="E8" s="18"/>
       <c r="F8" s="7">
@@ -9720,11 +10274,11 @@
       </c>
       <c r="H8" s="8">
         <f>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I8" s="19">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.63135593220338981</v>
+        <v>0.63291139240506333</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9741,7 +10295,7 @@
       </c>
       <c r="D9" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2372881355932203E-3</v>
+        <v>4.2194092827004216E-3</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="26"/>
@@ -9750,7 +10304,7 @@
       </c>
       <c r="H9" s="17">
         <f>SUBTOTAL(109,Table2[عدد الخدمات])</f>
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I9" s="21"/>
     </row>
@@ -9768,7 +10322,7 @@
       </c>
       <c r="D10" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>5.5084745762711863E-2</v>
+        <v>5.4852320675105488E-2</v>
       </c>
       <c r="E10" s="18"/>
       <c r="F10" s="25"/>
@@ -9790,7 +10344,7 @@
       </c>
       <c r="D11" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4745762711864406E-3</v>
+        <v>8.4388185654008432E-3</v>
       </c>
       <c r="E11" s="18"/>
       <c r="F11" s="9" t="s">
@@ -9820,7 +10374,7 @@
       </c>
       <c r="D12" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4745762711864406E-3</v>
+        <v>8.4388185654008432E-3</v>
       </c>
       <c r="E12" s="18"/>
       <c r="F12" s="12">
@@ -9835,7 +10389,7 @@
       </c>
       <c r="I12" s="15">
         <f>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</f>
-        <v>7.2033898305084748E-2</v>
+        <v>7.1729957805907171E-2</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.35">
@@ -9852,7 +10406,7 @@
       </c>
       <c r="D13" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2711864406779662E-2</v>
+        <v>1.2658227848101266E-2</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="12">
@@ -9863,11 +10417,11 @@
       </c>
       <c r="H13" s="13">
         <f>COUNTIF(Table1[نوع العمل],Table4[[#This Row],[نوع العمل]])</f>
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I13" s="15">
         <f>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</f>
-        <v>0.92796610169491522</v>
+        <v>0.92827004219409281</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.35">
@@ -9884,7 +10438,7 @@
       </c>
       <c r="D14" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4745762711864406E-3</v>
+        <v>8.4388185654008432E-3</v>
       </c>
       <c r="E14" s="18"/>
       <c r="F14" s="12"/>
@@ -9893,7 +10447,7 @@
       </c>
       <c r="H14" s="13">
         <f>SUBTOTAL(109,Table4[عدد الخدمات])</f>
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I14" s="14"/>
     </row>
@@ -9911,7 +10465,7 @@
       </c>
       <c r="D15" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2372881355932203E-3</v>
+        <v>4.2194092827004216E-3</v>
       </c>
       <c r="E15" s="18"/>
     </row>
@@ -9929,7 +10483,7 @@
       </c>
       <c r="D16" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>6.7796610169491525E-2</v>
+        <v>6.7510548523206745E-2</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="27" t="s">
@@ -9959,7 +10513,7 @@
       </c>
       <c r="D17" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2372881355932203E-3</v>
+        <v>4.2194092827004216E-3</v>
       </c>
       <c r="E17" s="18"/>
       <c r="F17" s="29">
@@ -9975,7 +10529,7 @@
       </c>
       <c r="I17" s="32">
         <f>H17/SUM(Table3[عدد الخدمات])</f>
-        <v>0.1059322033898305</v>
+        <v>0.10548523206751055</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9992,7 +10546,7 @@
       </c>
       <c r="D18" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2711864406779662E-2</v>
+        <v>1.2658227848101266E-2</v>
       </c>
       <c r="E18" s="18"/>
       <c r="F18" s="29">
@@ -10007,7 +10561,7 @@
       </c>
       <c r="I18" s="16">
         <f>H18/SUM(Table3[عدد الخدمات])</f>
-        <v>9.7457627118644072E-2</v>
+        <v>9.7046413502109699E-2</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10024,7 +10578,7 @@
       </c>
       <c r="D19" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1186440677966101E-2</v>
+        <v>2.1097046413502109E-2</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="29">
@@ -10039,7 +10593,7 @@
       </c>
       <c r="I19" s="32">
         <f>H19/SUM(Table3[عدد الخدمات])</f>
-        <v>6.7796610169491525E-2</v>
+        <v>6.7510548523206745E-2</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10056,7 +10610,7 @@
       </c>
       <c r="D20" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2372881355932203E-3</v>
+        <v>4.2194092827004216E-3</v>
       </c>
       <c r="E20" s="18"/>
       <c r="F20" s="33"/>
@@ -10083,7 +10637,7 @@
       </c>
       <c r="D21" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4745762711864406E-3</v>
+        <v>8.4388185654008432E-3</v>
       </c>
       <c r="E21" s="18"/>
     </row>
@@ -10101,7 +10655,7 @@
       </c>
       <c r="D22" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4745762711864406E-3</v>
+        <v>8.4388185654008432E-3</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="27" t="s">
@@ -10131,7 +10685,7 @@
       </c>
       <c r="D23" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.9661016949152543E-2</v>
+        <v>2.9535864978902954E-2</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="29">
@@ -10147,7 +10701,7 @@
       </c>
       <c r="I23" s="32">
         <f>H23/SUM(Table3[عدد الخدمات])</f>
-        <v>4.2372881355932203E-3</v>
+        <v>4.2194092827004216E-3</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10164,7 +10718,7 @@
       </c>
       <c r="D24" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.5423728813559324E-2</v>
+        <v>2.5316455696202531E-2</v>
       </c>
       <c r="E24" s="18"/>
       <c r="F24" s="29">
@@ -10179,7 +10733,7 @@
       </c>
       <c r="I24" s="16">
         <f>H24/SUM(Table3[عدد الخدمات])</f>
-        <v>4.2372881355932203E-3</v>
+        <v>4.2194092827004216E-3</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10196,7 +10750,7 @@
       </c>
       <c r="D25" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.8135593220338986E-2</v>
+        <v>3.7974683544303799E-2</v>
       </c>
       <c r="E25" s="18"/>
       <c r="F25" s="29">
@@ -10211,7 +10765,7 @@
       </c>
       <c r="I25" s="32">
         <f>H25/SUM(Table3[عدد الخدمات])</f>
-        <v>4.2372881355932203E-3</v>
+        <v>4.2194092827004216E-3</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10228,7 +10782,7 @@
       </c>
       <c r="D26" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>0.1059322033898305</v>
+        <v>0.10548523206751055</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="33"/>
@@ -10255,7 +10809,7 @@
       </c>
       <c r="D27" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2372881355932203E-3</v>
+        <v>4.2194092827004216E-3</v>
       </c>
       <c r="E27" s="18"/>
     </row>
@@ -10273,7 +10827,7 @@
       </c>
       <c r="D28" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.8135593220338986E-2</v>
+        <v>3.7974683544303799E-2</v>
       </c>
       <c r="E28" s="18"/>
     </row>
@@ -10291,7 +10845,7 @@
       </c>
       <c r="D29" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1186440677966101E-2</v>
+        <v>2.1097046413502109E-2</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10308,7 +10862,7 @@
       </c>
       <c r="D30" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.9661016949152543E-2</v>
+        <v>2.9535864978902954E-2</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10325,7 +10879,7 @@
       </c>
       <c r="D31" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.6949152542372881E-2</v>
+        <v>1.6877637130801686E-2</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -10342,7 +10896,7 @@
       </c>
       <c r="D32" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1186440677966101E-2</v>
+        <v>2.1097046413502109E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10359,7 +10913,7 @@
       </c>
       <c r="D33" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2711864406779662E-2</v>
+        <v>1.2658227848101266E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10376,7 +10930,7 @@
       </c>
       <c r="D34" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2372881355932202E-2</v>
+        <v>4.2194092827004218E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10393,7 +10947,7 @@
       </c>
       <c r="D35" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4745762711864406E-3</v>
+        <v>8.4388185654008432E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10410,7 +10964,7 @@
       </c>
       <c r="D36" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2372881355932203E-3</v>
+        <v>4.2194092827004216E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10427,7 +10981,7 @@
       </c>
       <c r="D37" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.8135593220338986E-2</v>
+        <v>3.7974683544303799E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10444,7 +10998,7 @@
       </c>
       <c r="D38" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.8135593220338986E-2</v>
+        <v>3.7974683544303799E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10457,11 +11011,11 @@
       </c>
       <c r="C39" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D39" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.6610169491525424E-2</v>
+        <v>5.0632911392405063E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10478,7 +11032,7 @@
       </c>
       <c r="D40" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2372881355932203E-3</v>
+        <v>4.2194092827004216E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10495,7 +11049,7 @@
       </c>
       <c r="D41" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.7457627118644072E-2</v>
+        <v>9.7046413502109699E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -10505,11 +11059,11 @@
       </c>
       <c r="C42" s="8">
         <f>SUBTOTAL(109,Table3[عدد الخدمات])</f>
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D42" s="20">
         <f>SUBTOTAL(109,Table3[النسبة المئوية])</f>
-        <v>0.99999999999999978</v>
+        <v>0.99999999999999989</v>
       </c>
     </row>
   </sheetData>

--- a/الخدمات.xlsx
+++ b/الخدمات.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a843af4fc71c607/Desktop/JavaScript codes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDTC\Desktop\JavaScript-codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3447" documentId="11_6D1415C555E27CE26E339E56ADDC14C75C28AAF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A91B43B-50A1-436F-9000-D22321047410}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C02B2B-39EC-44AF-80AB-B20C0F454EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="معلومات الخدمات" sheetId="1" r:id="rId1"/>
@@ -1984,17 +1984,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="71">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="70">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2962,479 +2952,6 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
         <right/>
         <top style="thin">
           <color indexed="64"/>
@@ -3707,6 +3224,479 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3720,62 +3710,65 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G239" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G234">
-    <sortCondition ref="B2:B234"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G239" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68">
+  <autoFilter ref="A1:G239" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="الهيئة الوطنية للرقابة النووية والاشعاعية والكيميائية والبايولوجية"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G239">
+    <sortCondition ref="B2:B239"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{20FD99FD-87DB-4DD1-989A-014AAE8F25F6}" name="ت." dataDxfId="54" totalsRowDxfId="53">
+    <tableColumn id="1" xr3:uid="{20FD99FD-87DB-4DD1-989A-014AAE8F25F6}" name="ت." dataDxfId="66" totalsRowDxfId="65">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F323E4AC-F323-4F97-9904-326D9949B165}" name="رقم الخدمة" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{58A3CC8C-66BF-4DA6-B0EF-C7F43089C5C0}" name="اسم الخدمة" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{176DB514-0824-46BC-9146-CAA89D7A742F}" name="جهة الخدمة" dataDxfId="48" totalsRowDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{E4173C63-A839-4611-8E53-7B3AE2F439DB}" name="نوع الجهة" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{C01A4E12-3E16-4DE9-86B3-69F70894487E}" name="نوع العمل" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{3481871F-BF9F-4C45-AC54-67A9AF362483}" name="اسم الملف" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{F323E4AC-F323-4F97-9904-326D9949B165}" name="رقم الخدمة" dataDxfId="64" totalsRowDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{58A3CC8C-66BF-4DA6-B0EF-C7F43089C5C0}" name="اسم الخدمة" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{176DB514-0824-46BC-9146-CAA89D7A742F}" name="جهة الخدمة" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{E4173C63-A839-4611-8E53-7B3AE2F439DB}" name="نوع الجهة" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{C01A4E12-3E16-4DE9-86B3-69F70894487E}" name="نوع العمل" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{3481871F-BF9F-4C45-AC54-67A9AF362483}" name="اسم الملف" dataDxfId="54" totalsRowDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{84F97999-FBC9-427B-AC68-DAFBADA61BB8}" name="Table5" displayName="Table5" ref="A1:H6" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67" totalsRowBorderDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{84F97999-FBC9-427B-AC68-DAFBADA61BB8}" name="Table5" displayName="Table5" ref="A1:H6" totalsRowShown="0" headerRowDxfId="52" dataDxfId="50" headerRowBorderDxfId="51" tableBorderDxfId="49" totalsRowBorderDxfId="48">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{69E53D5C-73E1-4C2D-A2FF-8B09CE7A5D9B}" name="ت." dataDxfId="65">
+    <tableColumn id="1" xr3:uid="{69E53D5C-73E1-4C2D-A2FF-8B09CE7A5D9B}" name="ت." dataDxfId="47">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EBAAD0E3-6F6D-4DE2-A8C7-BC5A0EEE6FE2}" name="رقم الخدمة" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{0BCF7553-361D-472A-8D6B-445844D28E52}" name="اسم الخدمة" dataDxfId="63"/>
-    <tableColumn id="4" xr3:uid="{3E2F9AA3-02D8-4C6F-8CBA-BA47686A8C20}" name="جهة الخدمة" dataDxfId="62"/>
-    <tableColumn id="5" xr3:uid="{9F37D9B7-7A9A-4709-8DFC-E6579BBF5270}" name="نوع الجهة" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{2DD6D84B-0F1F-4F7E-BFC9-49CC99A8B055}" name="نوع العمل" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{97CE7C95-A47D-44C9-B115-777267316E94}" name="اسم الملف" dataDxfId="59"/>
-    <tableColumn id="7" xr3:uid="{2C0E9C57-3204-4A1B-B24D-2DE53DDD9D13}" name="مكان الدفع" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{EBAAD0E3-6F6D-4DE2-A8C7-BC5A0EEE6FE2}" name="رقم الخدمة" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{0BCF7553-361D-472A-8D6B-445844D28E52}" name="اسم الخدمة" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{3E2F9AA3-02D8-4C6F-8CBA-BA47686A8C20}" name="جهة الخدمة" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{9F37D9B7-7A9A-4709-8DFC-E6579BBF5270}" name="نوع الجهة" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{2DD6D84B-0F1F-4F7E-BFC9-49CC99A8B055}" name="نوع العمل" dataDxfId="42"/>
+    <tableColumn id="10" xr3:uid="{97CE7C95-A47D-44C9-B115-777267316E94}" name="اسم الملف" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{2C0E9C57-3204-4A1B-B24D-2DE53DDD9D13}" name="مكان الدفع" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="40" dataDxfId="38" totalsRowDxfId="37" headerRowBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="39" dataDxfId="37" totalsRowDxfId="36" headerRowBorderDxfId="38">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F2:I8">
     <sortCondition ref="G2:G8"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FDC31943-D832-4BCF-8A6F-51F74847839D}" name="ت." dataDxfId="36" totalsRowDxfId="35">
+    <tableColumn id="1" xr3:uid="{FDC31943-D832-4BCF-8A6F-51F74847839D}" name="ت." dataDxfId="35" totalsRowDxfId="34">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D6F61CFE-6FB5-4088-802C-280AB03DDC3F}" name="نوع الجهة" totalsRowLabel="المجموع" dataDxfId="34" totalsRowDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{819F64F0-7B30-437C-8552-96E1BA009158}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
+    <tableColumn id="2" xr3:uid="{D6F61CFE-6FB5-4088-802C-280AB03DDC3F}" name="نوع الجهة" totalsRowLabel="المجموع" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{819F64F0-7B30-437C-8552-96E1BA009158}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
       <calculatedColumnFormula>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D928E8D0-BE48-4700-B3FA-A3A0C6ED8D95}" name="النسبة المئوية" dataDxfId="30" totalsRowDxfId="29" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{D928E8D0-BE48-4700-B3FA-A3A0C6ED8D95}" name="النسبة المئوية" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Percent">
       <calculatedColumnFormula>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3784,19 +3777,19 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D42" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D42" totalsRowCount="1" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D41">
     <sortCondition ref="B2:B41"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{04CB5523-1DF6-4CA0-AC24-1D21F85D9F94}" name="ت." dataDxfId="23" totalsRowDxfId="22">
+    <tableColumn id="1" xr3:uid="{04CB5523-1DF6-4CA0-AC24-1D21F85D9F94}" name="ت." dataDxfId="22" totalsRowDxfId="21">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{966ACB29-C086-4C8E-BD62-D0F9ECCCA301}" name="اسم الجهة" totalsRowLabel="المجموع" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{E47A3AE0-B7A7-44F8-8FA6-8FA757A3066F}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18">
+    <tableColumn id="2" xr3:uid="{966ACB29-C086-4C8E-BD62-D0F9ECCCA301}" name="اسم الجهة" totalsRowLabel="المجموع" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{E47A3AE0-B7A7-44F8-8FA6-8FA757A3066F}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="17">
       <calculatedColumnFormula>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0D34DEDD-061D-44F4-9DA6-86D41E4BDDB7}" name="النسبة المئوية" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{0D34DEDD-061D-44F4-9DA6-86D41E4BDDB7}" name="النسبة المئوية" totalsRowFunction="sum" dataDxfId="16" totalsRowDxfId="15" dataCellStyle="Percent">
       <calculatedColumnFormula>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3805,16 +3798,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="10" totalsRowDxfId="9">
+    <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="9" totalsRowDxfId="8">
       <calculatedColumnFormula>ROW()-11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4A8E3EC9-46C6-46A2-85BB-E7D02B7ABF90}" name="نوع العمل" totalsRowLabel="المجموع" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{140AD779-6235-4A33-848F-7CF18BA55E33}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="5">
+    <tableColumn id="2" xr3:uid="{4A8E3EC9-46C6-46A2-85BB-E7D02B7ABF90}" name="نوع العمل" totalsRowLabel="المجموع" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{140AD779-6235-4A33-848F-7CF18BA55E33}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4">
       <calculatedColumnFormula>COUNTIF(Table1[نوع العمل],Table4[[#This Row],[نوع العمل]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CD921388-F9B8-4CDD-A07C-FBB8C0ABF589}" name="النسبة المئوية" dataDxfId="4" totalsRowDxfId="3" dataCellStyle="Percent">
+    <tableColumn id="4" xr3:uid="{CD921388-F9B8-4CDD-A07C-FBB8C0ABF589}" name="النسبة المئوية" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Percent">
       <calculatedColumnFormula>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4086,18 +4079,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G239"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="148.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="59.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="148.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="59.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4120,9 +4113,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <f t="shared" ref="A2:A65" si="0">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -4144,9 +4137,9 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="3">
@@ -4168,9 +4161,9 @@
         <v>382</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>3</v>
       </c>
       <c r="B4" s="3">
@@ -4192,9 +4185,9 @@
         <v>291</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>4</v>
       </c>
       <c r="B5" s="3">
@@ -4216,9 +4209,9 @@
         <v>10335</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>5</v>
       </c>
       <c r="B6" s="3">
@@ -4240,9 +4233,9 @@
         <v>312</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>6</v>
       </c>
       <c r="B7" s="3">
@@ -4264,9 +4257,9 @@
         <v>237</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>7</v>
       </c>
       <c r="B8" s="3">
@@ -4288,9 +4281,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>8</v>
       </c>
       <c r="B9" s="3">
@@ -4312,9 +4305,9 @@
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>9</v>
       </c>
       <c r="B10" s="3">
@@ -4336,9 +4329,9 @@
         <v>226</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>10</v>
       </c>
       <c r="B11" s="3">
@@ -4360,9 +4353,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>11</v>
       </c>
       <c r="B12" s="3">
@@ -4384,9 +4377,9 @@
         <v>227</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>12</v>
       </c>
       <c r="B13" s="3">
@@ -4408,9 +4401,9 @@
         <v>503</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>13</v>
       </c>
       <c r="B14" s="3">
@@ -4432,9 +4425,9 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>14</v>
       </c>
       <c r="B15" s="3">
@@ -4456,9 +4449,9 @@
         <v>481</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>15</v>
       </c>
       <c r="B16" s="3">
@@ -4480,9 +4473,9 @@
         <v>199</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>16</v>
       </c>
       <c r="B17" s="3">
@@ -4504,9 +4497,9 @@
         <v>10532</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>17</v>
       </c>
       <c r="B18" s="3">
@@ -4528,9 +4521,9 @@
         <v>10539</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>18</v>
       </c>
       <c r="B19" s="3">
@@ -4552,9 +4545,9 @@
         <v>10541</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>19</v>
       </c>
       <c r="B20" s="3">
@@ -4576,9 +4569,9 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>20</v>
       </c>
       <c r="B21" s="3">
@@ -4600,9 +4593,9 @@
         <v>10565</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>21</v>
       </c>
       <c r="B22" s="3">
@@ -4624,9 +4617,9 @@
         <v>10568</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>22</v>
       </c>
       <c r="B23" s="3">
@@ -4648,9 +4641,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>23</v>
       </c>
       <c r="B24" s="3">
@@ -4672,9 +4665,9 @@
         <v>445</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>24</v>
       </c>
       <c r="B25" s="3">
@@ -4696,9 +4689,9 @@
         <v>10611</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>25</v>
       </c>
       <c r="B26" s="3">
@@ -4720,9 +4713,9 @@
         <v>10630</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>26</v>
       </c>
       <c r="B27" s="3">
@@ -4744,9 +4737,9 @@
         <v>232</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>27</v>
       </c>
       <c r="B28" s="3">
@@ -4768,9 +4761,9 @@
         <v>10664</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>28</v>
       </c>
       <c r="B29" s="3">
@@ -4792,9 +4785,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>29</v>
       </c>
       <c r="B30" s="3">
@@ -4816,9 +4809,9 @@
         <v>10688</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>30</v>
       </c>
       <c r="B31" s="3">
@@ -4840,9 +4833,9 @@
         <v>361</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>31</v>
       </c>
       <c r="B32" s="3">
@@ -4864,9 +4857,9 @@
         <v>238</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>32</v>
       </c>
       <c r="B33" s="3">
@@ -4888,9 +4881,9 @@
         <v>163</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>33</v>
       </c>
       <c r="B34" s="3">
@@ -4912,9 +4905,9 @@
         <v>363</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>34</v>
       </c>
       <c r="B35" s="3">
@@ -4936,9 +4929,9 @@
         <v>404</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>35</v>
       </c>
       <c r="B36" s="3">
@@ -4960,9 +4953,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>36</v>
       </c>
       <c r="B37" s="3">
@@ -4984,9 +4977,9 @@
         <v>321</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>37</v>
       </c>
       <c r="B38" s="3">
@@ -5008,9 +5001,9 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>38</v>
       </c>
       <c r="B39" s="3">
@@ -5032,9 +5025,9 @@
         <v>262</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>39</v>
       </c>
       <c r="B40" s="3">
@@ -5056,9 +5049,9 @@
         <v>236</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>40</v>
       </c>
       <c r="B41" s="3">
@@ -5080,9 +5073,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>41</v>
       </c>
       <c r="B42" s="3">
@@ -5104,9 +5097,9 @@
         <v>234</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>42</v>
       </c>
       <c r="B43" s="3">
@@ -5128,9 +5121,9 @@
         <v>376</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>43</v>
       </c>
       <c r="B44" s="3">
@@ -5152,9 +5145,9 @@
         <v>215</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>44</v>
       </c>
       <c r="B45" s="3">
@@ -5176,9 +5169,9 @@
         <v>261</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>45</v>
       </c>
       <c r="B46" s="3">
@@ -5200,9 +5193,9 @@
         <v>170</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>46</v>
       </c>
       <c r="B47" s="3">
@@ -5224,9 +5217,9 @@
         <v>171</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>47</v>
       </c>
       <c r="B48" s="3">
@@ -5248,9 +5241,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>48</v>
       </c>
       <c r="B49" s="3">
@@ -5272,9 +5265,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>49</v>
       </c>
       <c r="B50" s="3">
@@ -5296,9 +5289,9 @@
         <v>193</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>50</v>
       </c>
       <c r="B51" s="3">
@@ -5320,9 +5313,9 @@
         <v>172</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>51</v>
       </c>
       <c r="B52" s="3">
@@ -5344,9 +5337,9 @@
         <v>197</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>52</v>
       </c>
       <c r="B53" s="3">
@@ -5368,9 +5361,9 @@
         <v>174</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>53</v>
       </c>
       <c r="B54" s="3">
@@ -5392,9 +5385,9 @@
         <v>201</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>54</v>
       </c>
       <c r="B55" s="3">
@@ -5416,9 +5409,9 @@
         <v>477</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>55</v>
       </c>
       <c r="B56" s="3">
@@ -5440,9 +5433,9 @@
         <v>21076</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>56</v>
       </c>
       <c r="B57" s="3">
@@ -5464,9 +5457,9 @@
         <v>179</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>57</v>
       </c>
       <c r="B58" s="3">
@@ -5488,9 +5481,9 @@
         <v>218</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>58</v>
       </c>
       <c r="B59" s="3">
@@ -5512,9 +5505,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>59</v>
       </c>
       <c r="B60" s="3">
@@ -5536,9 +5529,9 @@
         <v>302</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>60</v>
       </c>
       <c r="B61" s="3">
@@ -5560,9 +5553,9 @@
         <v>229</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>61</v>
       </c>
       <c r="B62" s="3">
@@ -5584,9 +5577,9 @@
         <v>267</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>62</v>
       </c>
       <c r="B63" s="3">
@@ -5608,9 +5601,9 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>63</v>
       </c>
       <c r="B64" s="3">
@@ -5632,9 +5625,9 @@
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>64</v>
       </c>
       <c r="B65" s="3">
@@ -5656,9 +5649,9 @@
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
-        <f t="shared" ref="A66:A129" si="1">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>65</v>
       </c>
       <c r="B66" s="3">
@@ -5680,9 +5673,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>66</v>
       </c>
       <c r="B67" s="3">
@@ -5704,9 +5697,9 @@
         <v>258</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>67</v>
       </c>
       <c r="B68" s="3">
@@ -5728,9 +5721,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>68</v>
       </c>
       <c r="B69" s="3">
@@ -5752,9 +5745,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>69</v>
       </c>
       <c r="B70" s="3">
@@ -5776,9 +5769,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>70</v>
       </c>
       <c r="B71" s="3">
@@ -5800,9 +5793,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>71</v>
       </c>
       <c r="B72" s="3">
@@ -5824,9 +5817,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>72</v>
       </c>
       <c r="B73" s="3">
@@ -5848,9 +5841,9 @@
         <v>437</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="3">
@@ -5872,9 +5865,9 @@
         <v>168</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>74</v>
       </c>
       <c r="B75" s="3">
@@ -5896,9 +5889,9 @@
         <v>259</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>75</v>
       </c>
       <c r="B76" s="3">
@@ -5920,9 +5913,9 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>76</v>
       </c>
       <c r="B77" s="3">
@@ -5944,9 +5937,9 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>77</v>
       </c>
       <c r="B78" s="3">
@@ -5968,9 +5961,9 @@
         <v>256</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>78</v>
       </c>
       <c r="B79" s="3">
@@ -5992,9 +5985,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>79</v>
       </c>
       <c r="B80" s="3">
@@ -6016,9 +6009,9 @@
         <v>252</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>80</v>
       </c>
       <c r="B81" s="3">
@@ -6040,9 +6033,9 @@
         <v>176</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>81</v>
       </c>
       <c r="B82" s="3">
@@ -6064,9 +6057,9 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>82</v>
       </c>
       <c r="B83" s="3">
@@ -6088,9 +6081,9 @@
         <v>285</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>83</v>
       </c>
       <c r="B84" s="3">
@@ -6112,9 +6105,9 @@
         <v>183</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>84</v>
       </c>
       <c r="B85" s="3">
@@ -6136,9 +6129,9 @@
         <v>220</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>85</v>
       </c>
       <c r="B86" s="3">
@@ -6160,9 +6153,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>86</v>
       </c>
       <c r="B87" s="3">
@@ -6184,9 +6177,9 @@
         <v>245</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>87</v>
       </c>
       <c r="B88" s="3">
@@ -6208,9 +6201,9 @@
         <v>298</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>88</v>
       </c>
       <c r="B89" s="3">
@@ -6232,9 +6225,9 @@
         <v>296</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>89</v>
       </c>
       <c r="B90" s="3">
@@ -6256,9 +6249,9 @@
         <v>178</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>90</v>
       </c>
       <c r="B91" s="3">
@@ -6280,9 +6273,9 @@
         <v>270</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>91</v>
       </c>
       <c r="B92" s="3">
@@ -6304,9 +6297,9 @@
         <v>265</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>92</v>
       </c>
       <c r="B93" s="3">
@@ -6328,9 +6321,9 @@
         <v>355</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>93</v>
       </c>
       <c r="B94" s="3">
@@ -6352,9 +6345,9 @@
         <v>257</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>94</v>
       </c>
       <c r="B95" s="3">
@@ -6376,9 +6369,9 @@
         <v>264</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>95</v>
       </c>
       <c r="B96" s="3">
@@ -6400,9 +6393,9 @@
         <v>202</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>96</v>
       </c>
       <c r="B97" s="3">
@@ -6424,9 +6417,9 @@
         <v>253</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>97</v>
       </c>
       <c r="B98" s="3">
@@ -6448,9 +6441,9 @@
         <v>195</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>98</v>
       </c>
       <c r="B99" s="3">
@@ -6472,9 +6465,9 @@
         <v>230</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>99</v>
       </c>
       <c r="B100" s="3">
@@ -6496,9 +6489,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>100</v>
       </c>
       <c r="B101" s="3">
@@ -6520,9 +6513,9 @@
         <v>222</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>101</v>
       </c>
       <c r="B102" s="3">
@@ -6544,9 +6537,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>102</v>
       </c>
       <c r="B103" s="3">
@@ -6568,9 +6561,9 @@
         <v>254</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>103</v>
       </c>
       <c r="B104" s="3">
@@ -6592,9 +6585,9 @@
         <v>181</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>104</v>
       </c>
       <c r="B105" s="3">
@@ -6616,9 +6609,9 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>105</v>
       </c>
       <c r="B106" s="3">
@@ -6640,9 +6633,9 @@
         <v>339</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>106</v>
       </c>
       <c r="B107" s="3">
@@ -6664,9 +6657,9 @@
         <v>203</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>107</v>
       </c>
       <c r="B108" s="3">
@@ -6688,9 +6681,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>108</v>
       </c>
       <c r="B109" s="3">
@@ -6712,9 +6705,9 @@
         <v>443</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>109</v>
       </c>
       <c r="B110" s="3">
@@ -6736,9 +6729,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>110</v>
       </c>
       <c r="B111" s="3">
@@ -6760,9 +6753,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>111</v>
       </c>
       <c r="B112" s="3">
@@ -6784,9 +6777,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>112</v>
       </c>
       <c r="B113" s="3">
@@ -6808,9 +6801,9 @@
         <v>190</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>113</v>
       </c>
       <c r="B114" s="3">
@@ -6832,9 +6825,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>114</v>
       </c>
       <c r="B115" s="3">
@@ -6856,9 +6849,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>115</v>
       </c>
       <c r="B116" s="3">
@@ -6880,9 +6873,9 @@
         <v>217</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>116</v>
       </c>
       <c r="B117" s="3">
@@ -6904,9 +6897,9 @@
         <v>216</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>117</v>
       </c>
       <c r="B118" s="3">
@@ -6928,9 +6921,9 @@
         <v>213</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>118</v>
       </c>
       <c r="B119" s="3">
@@ -6952,9 +6945,9 @@
         <v>182</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>119</v>
       </c>
       <c r="B120" s="3">
@@ -6976,9 +6969,9 @@
         <v>196</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>120</v>
       </c>
       <c r="B121" s="3">
@@ -7000,9 +6993,9 @@
         <v>157</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>121</v>
       </c>
       <c r="B122" s="3">
@@ -7024,9 +7017,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>122</v>
       </c>
       <c r="B123" s="3">
@@ -7048,9 +7041,9 @@
         <v>315</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>123</v>
       </c>
       <c r="B124" s="3">
@@ -7072,9 +7065,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>124</v>
       </c>
       <c r="B125" s="3">
@@ -7096,9 +7089,9 @@
         <v>191</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>125</v>
       </c>
       <c r="B126" s="3">
@@ -7120,9 +7113,9 @@
         <v>241</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>126</v>
       </c>
       <c r="B127" s="3">
@@ -7144,9 +7137,9 @@
         <v>263</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>127</v>
       </c>
       <c r="B128" s="3">
@@ -7168,9 +7161,9 @@
         <v>418</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>128</v>
       </c>
       <c r="B129" s="3">
@@ -7192,9 +7185,9 @@
         <v>414</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
-        <f t="shared" ref="A130:A193" si="2">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>129</v>
       </c>
       <c r="B130" s="3">
@@ -7216,9 +7209,9 @@
         <v>406</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>130</v>
       </c>
       <c r="B131" s="3">
@@ -7240,9 +7233,9 @@
         <v>244</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>131</v>
       </c>
       <c r="B132" s="3">
@@ -7264,9 +7257,9 @@
         <v>169</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>132</v>
       </c>
       <c r="B133" s="3">
@@ -7288,9 +7281,9 @@
         <v>243</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>133</v>
       </c>
       <c r="B134" s="3">
@@ -7312,9 +7305,9 @@
         <v>408</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>134</v>
       </c>
       <c r="B135" s="3">
@@ -7336,9 +7329,9 @@
         <v>410</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>135</v>
       </c>
       <c r="B136" s="3">
@@ -7360,9 +7353,9 @@
         <v>416</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>136</v>
       </c>
       <c r="B137" s="3">
@@ -7384,9 +7377,9 @@
         <v>248</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>137</v>
       </c>
       <c r="B138" s="3">
@@ -7408,9 +7401,9 @@
         <v>247</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>138</v>
       </c>
       <c r="B139" s="3">
@@ -7432,9 +7425,9 @@
         <v>209</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>139</v>
       </c>
       <c r="B140" s="3">
@@ -7456,9 +7449,9 @@
         <v>158</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>140</v>
       </c>
       <c r="B141" s="3">
@@ -7480,9 +7473,9 @@
         <v>214</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>141</v>
       </c>
       <c r="B142" s="3">
@@ -7504,9 +7497,9 @@
         <v>412</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>142</v>
       </c>
       <c r="B143" s="3">
@@ -7528,9 +7521,9 @@
         <v>223</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>143</v>
       </c>
       <c r="B144" s="3">
@@ -7552,9 +7545,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>144</v>
       </c>
       <c r="B145" s="3">
@@ -7576,9 +7569,9 @@
         <v>332</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>145</v>
       </c>
       <c r="B146" s="3">
@@ -7600,9 +7593,9 @@
         <v>330</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>146</v>
       </c>
       <c r="B147" s="3">
@@ -7624,9 +7617,9 @@
         <v>473</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>147</v>
       </c>
       <c r="B148" s="3">
@@ -7648,9 +7641,9 @@
         <v>219</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>148</v>
       </c>
       <c r="B149" s="3">
@@ -7672,9 +7665,9 @@
         <v>400</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>149</v>
       </c>
       <c r="B150" s="3">
@@ -7696,9 +7689,9 @@
         <v>475</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>150</v>
       </c>
       <c r="B151" s="3">
@@ -7720,9 +7713,9 @@
         <v>287</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>151</v>
       </c>
       <c r="B152" s="3">
@@ -7744,9 +7737,9 @@
         <v>224</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>152</v>
       </c>
       <c r="B153" s="3">
@@ -7768,9 +7761,9 @@
         <v>335</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>153</v>
       </c>
       <c r="B154" s="3">
@@ -7792,9 +7785,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>154</v>
       </c>
       <c r="B155" s="3">
@@ -7816,9 +7809,9 @@
         <v>398</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>155</v>
       </c>
       <c r="B156" s="3">
@@ -7840,9 +7833,9 @@
         <v>396</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>156</v>
       </c>
       <c r="B157" s="3">
@@ -7864,9 +7857,9 @@
         <v>394</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>157</v>
       </c>
       <c r="B158" s="3">
@@ -7888,9 +7881,9 @@
         <v>274</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>158</v>
       </c>
       <c r="B159" s="3">
@@ -7912,9 +7905,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>159</v>
       </c>
       <c r="B160" s="3">
@@ -7936,9 +7929,9 @@
         <v>402</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>160</v>
       </c>
       <c r="B161" s="3">
@@ -7960,9 +7953,9 @@
         <v>391</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>161</v>
       </c>
       <c r="B162" s="3">
@@ -7984,9 +7977,9 @@
         <v>21612</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>162</v>
       </c>
       <c r="B163" s="3">
@@ -8008,9 +8001,9 @@
         <v>389</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>163</v>
       </c>
       <c r="B164" s="3">
@@ -8032,9 +8025,9 @@
         <v>387</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>164</v>
       </c>
       <c r="B165" s="3">
@@ -8056,9 +8049,9 @@
         <v>392</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>165</v>
       </c>
       <c r="B166" s="3">
@@ -8080,9 +8073,9 @@
         <v>384</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>166</v>
       </c>
       <c r="B167" s="3">
@@ -8104,9 +8097,9 @@
         <v>465</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>167</v>
       </c>
       <c r="B168" s="3">
@@ -8128,9 +8121,9 @@
         <v>372</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>168</v>
       </c>
       <c r="B169" s="3">
@@ -8152,9 +8145,9 @@
         <v>21626</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>169</v>
       </c>
       <c r="B170" s="3">
@@ -8176,9 +8169,9 @@
         <v>370</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>170</v>
       </c>
       <c r="B171" s="3">
@@ -8200,9 +8193,9 @@
         <v>310</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>171</v>
       </c>
       <c r="B172" s="3">
@@ -8224,9 +8217,9 @@
         <v>21633</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>172</v>
       </c>
       <c r="B173" s="3">
@@ -8248,9 +8241,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>173</v>
       </c>
       <c r="B174" s="3">
@@ -8272,9 +8265,9 @@
         <v>281</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>174</v>
       </c>
       <c r="B175" s="3">
@@ -8296,9 +8289,9 @@
         <v>251</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>175</v>
       </c>
       <c r="B176" s="3">
@@ -8320,9 +8313,9 @@
         <v>327</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>176</v>
       </c>
       <c r="B177" s="3">
@@ -8344,9 +8337,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>177</v>
       </c>
       <c r="B178" s="3">
@@ -8368,9 +8361,9 @@
         <v>344</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>178</v>
       </c>
       <c r="B179" s="3">
@@ -8392,9 +8385,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>179</v>
       </c>
       <c r="B180" s="3">
@@ -8416,9 +8409,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>180</v>
       </c>
       <c r="B181" s="3">
@@ -8440,9 +8433,9 @@
         <v>308</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>181</v>
       </c>
       <c r="B182" s="3">
@@ -8464,9 +8457,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>182</v>
       </c>
       <c r="B183" s="3">
@@ -8488,9 +8481,9 @@
         <v>289</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>183</v>
       </c>
       <c r="B184" s="3">
@@ -8512,9 +8505,9 @@
         <v>21682</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A185" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>184</v>
       </c>
       <c r="B185" s="3">
@@ -8536,9 +8529,9 @@
         <v>21695</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>185</v>
       </c>
       <c r="B186" s="3">
@@ -8560,9 +8553,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>186</v>
       </c>
       <c r="B187" s="3">
@@ -8584,9 +8577,9 @@
         <v>459</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>187</v>
       </c>
       <c r="B188" s="3">
@@ -8608,9 +8601,9 @@
         <v>457</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>188</v>
       </c>
       <c r="B189" s="3">
@@ -8632,9 +8625,9 @@
         <v>350</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>189</v>
       </c>
       <c r="B190" s="3">
@@ -8656,9 +8649,9 @@
         <v>499</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>190</v>
       </c>
       <c r="B191" s="3">
@@ -8680,9 +8673,9 @@
         <v>368</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>191</v>
       </c>
       <c r="B192" s="3">
@@ -8704,9 +8697,9 @@
         <v>317</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>192</v>
       </c>
       <c r="B193" s="3">
@@ -8728,9 +8721,9 @@
         <v>337</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
-        <f t="shared" ref="A194:A234" si="3">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>193</v>
       </c>
       <c r="B194" s="3">
@@ -8752,9 +8745,9 @@
         <v>433</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>194</v>
       </c>
       <c r="B195" s="3">
@@ -8776,9 +8769,9 @@
         <v>348</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>195</v>
       </c>
       <c r="B196" s="3">
@@ -8800,9 +8793,9 @@
         <v>323</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>196</v>
       </c>
       <c r="B197" s="3">
@@ -8824,9 +8817,9 @@
         <v>352</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>197</v>
       </c>
       <c r="B198" s="3">
@@ -8848,9 +8841,9 @@
         <v>467</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>198</v>
       </c>
       <c r="B199" s="3">
@@ -8872,9 +8865,9 @@
         <v>492</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>199</v>
       </c>
       <c r="B200" s="3">
@@ -8896,9 +8889,9 @@
         <v>491</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>200</v>
       </c>
       <c r="B201" s="3">
@@ -8920,9 +8913,9 @@
         <v>469</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>201</v>
       </c>
       <c r="B202" s="3">
@@ -8944,9 +8937,9 @@
         <v>422</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>202</v>
       </c>
       <c r="B203" s="3">
@@ -8968,9 +8961,9 @@
         <v>357</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>203</v>
       </c>
       <c r="B204" s="3">
@@ -8992,9 +8985,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>204</v>
       </c>
       <c r="B205" s="3">
@@ -9016,9 +9009,9 @@
         <v>495</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>205</v>
       </c>
       <c r="B206" s="3">
@@ -9040,9 +9033,9 @@
         <v>359</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>206</v>
       </c>
       <c r="B207" s="3">
@@ -9064,9 +9057,9 @@
         <v>483</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>207</v>
       </c>
       <c r="B208" s="3">
@@ -9088,9 +9081,9 @@
         <v>447</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>208</v>
       </c>
       <c r="B209" s="3">
@@ -9112,9 +9105,9 @@
         <v>489</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>209</v>
       </c>
       <c r="B210" s="3">
@@ -9136,9 +9129,9 @@
         <v>380</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>210</v>
       </c>
       <c r="B211" s="3">
@@ -9160,9 +9153,9 @@
         <v>428</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>211</v>
       </c>
       <c r="B212" s="3">
@@ -9184,9 +9177,9 @@
         <v>461</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>212</v>
       </c>
       <c r="B213" s="3">
@@ -9208,9 +9201,9 @@
         <v>374</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>213</v>
       </c>
       <c r="B214" s="3">
@@ -9232,9 +9225,9 @@
         <v>455</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>214</v>
       </c>
       <c r="B215" s="3">
@@ -9256,136 +9249,136 @@
         <v>365</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>215</v>
       </c>
       <c r="B216" s="3">
+        <v>21799</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="3">
+        <f>ROW()-1</f>
+        <v>216</v>
+      </c>
+      <c r="B217" s="3">
         <v>21802</v>
       </c>
-      <c r="C216" s="3" t="s">
+      <c r="C217" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="D216" s="3" t="s">
+      <c r="D217" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E216" s="3" t="s">
+      <c r="E217" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F216" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G216" s="3" t="s">
+      <c r="F217" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G217" s="3" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A217" s="3">
-        <f t="shared" si="3"/>
-        <v>216</v>
-      </c>
-      <c r="B217" s="3">
+    <row r="218" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="3">
+        <f>ROW()-1</f>
+        <v>217</v>
+      </c>
+      <c r="B218" s="3">
         <v>21807</v>
       </c>
-      <c r="C217" s="3" t="s">
+      <c r="C218" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="D217" s="3" t="s">
+      <c r="D218" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E217" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F217" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G217" s="3" t="s">
+      <c r="E218" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G218" s="3" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A218" s="3">
-        <f t="shared" si="3"/>
-        <v>217</v>
-      </c>
-      <c r="B218" s="3">
+    <row r="219" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="3">
+        <f>ROW()-1</f>
+        <v>218</v>
+      </c>
+      <c r="B219" s="3">
         <v>21817</v>
       </c>
-      <c r="C218" s="3" t="s">
+      <c r="C219" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="D218" s="3" t="s">
+      <c r="D219" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E218" s="3" t="s">
+      <c r="E219" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F218" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G218" s="3" t="s">
+      <c r="F219" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G219" s="3" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A219" s="3">
-        <f t="shared" si="3"/>
-        <v>218</v>
-      </c>
-      <c r="B219" s="3">
+    <row r="220" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="3">
+        <f>ROW()-1</f>
+        <v>219</v>
+      </c>
+      <c r="B220" s="3">
         <v>21819</v>
       </c>
-      <c r="C219" s="3" t="s">
+      <c r="C220" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="D219" s="3" t="s">
+      <c r="D220" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="E219" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F219" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G219" s="3" t="s">
+      <c r="E220" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G220" s="3" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A220" s="3">
-        <f t="shared" si="3"/>
-        <v>219</v>
-      </c>
-      <c r="B220" s="3">
+    <row r="221" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="3">
+        <f>ROW()-1</f>
+        <v>220</v>
+      </c>
+      <c r="B221" s="3">
         <v>21829</v>
       </c>
-      <c r="C220" s="3" t="s">
+      <c r="C221" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="D220" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E220" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F220" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G220" s="3" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A221" s="3">
-        <f t="shared" si="3"/>
-        <v>220</v>
-      </c>
-      <c r="B221" s="3">
-        <v>21836</v>
-      </c>
-      <c r="C221" s="3" t="s">
-        <v>440</v>
       </c>
       <c r="D221" s="3" t="s">
         <v>35</v>
@@ -9397,370 +9390,370 @@
         <v>88</v>
       </c>
       <c r="G221" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="3">
+        <f>ROW()-1</f>
+        <v>221</v>
+      </c>
+      <c r="B222" s="3">
+        <v>21836</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G222" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A222" s="3">
-        <f t="shared" si="3"/>
-        <v>221</v>
-      </c>
-      <c r="B222" s="3">
+    <row r="223" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="3">
+        <f>ROW()-1</f>
+        <v>222</v>
+      </c>
+      <c r="B223" s="3">
         <v>21837</v>
       </c>
-      <c r="C222" s="3" t="s">
+      <c r="C223" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="D222" s="3" t="s">
+      <c r="D223" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="E222" s="3" t="s">
+      <c r="E223" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F222" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G222" s="3" t="s">
+      <c r="F223" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G223" s="3" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A223" s="3">
-        <f t="shared" si="3"/>
-        <v>222</v>
-      </c>
-      <c r="B223" s="3">
+    <row r="224" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="3">
+        <f>ROW()-1</f>
+        <v>223</v>
+      </c>
+      <c r="B224" s="3">
         <v>21839</v>
       </c>
-      <c r="C223" s="3" t="s">
+      <c r="C224" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="D223" s="3" t="s">
+      <c r="D224" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E223" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F223" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G223" s="3" t="s">
+      <c r="E224" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G224" s="3" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A224" s="3">
-        <f t="shared" si="3"/>
-        <v>223</v>
-      </c>
-      <c r="B224" s="3">
+    <row r="225" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="3">
+        <f>ROW()-1</f>
+        <v>224</v>
+      </c>
+      <c r="B225" s="3">
         <v>21840</v>
       </c>
-      <c r="C224" s="3" t="s">
+      <c r="C225" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="D224" s="3" t="s">
+      <c r="D225" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="E224" s="3" t="s">
+      <c r="E225" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F224" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G224" s="3" t="s">
+      <c r="F225" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G225" s="3" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A225" s="3">
-        <f t="shared" si="3"/>
-        <v>224</v>
-      </c>
-      <c r="B225" s="3">
+    <row r="226" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="3">
+        <f>ROW()-1</f>
+        <v>225</v>
+      </c>
+      <c r="B226" s="3">
         <v>21847</v>
       </c>
-      <c r="C225" s="3" t="s">
+      <c r="C226" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="D225" s="3" t="s">
+      <c r="D226" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E225" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F225" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G225" s="3" t="s">
+      <c r="E226" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G226" s="3" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A226" s="3">
-        <f t="shared" si="3"/>
-        <v>225</v>
-      </c>
-      <c r="B226" s="3">
+    <row r="227" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="3">
+        <f>ROW()-1</f>
+        <v>226</v>
+      </c>
+      <c r="B227" s="3">
         <v>21850</v>
       </c>
-      <c r="C226" s="3" t="s">
+      <c r="C227" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="D226" s="3" t="s">
+      <c r="D227" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E226" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F226" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G226" s="3" t="s">
+      <c r="E227" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G227" s="3" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A227" s="3">
-        <f t="shared" si="3"/>
-        <v>226</v>
-      </c>
-      <c r="B227" s="3">
+    <row r="228" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="3">
+        <f>ROW()-1</f>
+        <v>227</v>
+      </c>
+      <c r="B228" s="3">
         <v>21851</v>
       </c>
-      <c r="C227" s="3" t="s">
+      <c r="C228" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="D227" s="3" t="s">
+      <c r="D228" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E227" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F227" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G227" s="3" t="s">
+      <c r="E228" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G228" s="3" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A228" s="3">
-        <f t="shared" si="3"/>
-        <v>227</v>
-      </c>
-      <c r="B228" s="3">
+    <row r="229" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="3">
+        <f>ROW()-1</f>
+        <v>228</v>
+      </c>
+      <c r="B229" s="3">
         <v>21858</v>
       </c>
-      <c r="C228" s="3" t="s">
+      <c r="C229" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="D228" s="3" t="s">
+      <c r="D229" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E228" s="3" t="s">
+      <c r="E229" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F228" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G228" s="3" t="s">
+      <c r="F229" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G229" s="3" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A229" s="3">
-        <f t="shared" si="3"/>
-        <v>228</v>
-      </c>
-      <c r="B229" s="3">
+    <row r="230" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="3">
+        <f>ROW()-1</f>
+        <v>229</v>
+      </c>
+      <c r="B230" s="3">
         <v>21863</v>
       </c>
-      <c r="C229" s="3" t="s">
+      <c r="C230" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="D229" s="3" t="s">
+      <c r="D230" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E229" s="3" t="s">
+      <c r="E230" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F229" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G229" s="3" t="s">
+      <c r="F230" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G230" s="3" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A230" s="3">
-        <f t="shared" si="3"/>
-        <v>229</v>
-      </c>
-      <c r="B230" s="3">
+    <row r="231" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="3">
+        <f>ROW()-1</f>
+        <v>230</v>
+      </c>
+      <c r="B231" s="3">
         <v>21864</v>
       </c>
-      <c r="C230" s="3" t="s">
+      <c r="C231" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="D230" s="3" t="s">
+      <c r="D231" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E230" s="3" t="s">
+      <c r="E231" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F230" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G230" s="3" t="s">
+      <c r="F231" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G231" s="3" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A231" s="3">
-        <f t="shared" si="3"/>
-        <v>230</v>
-      </c>
-      <c r="B231" s="3">
+    <row r="232" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="3">
+        <f>ROW()-1</f>
+        <v>231</v>
+      </c>
+      <c r="B232" s="3">
         <v>21877</v>
       </c>
-      <c r="C231" s="3" t="s">
+      <c r="C232" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="D231" s="3" t="s">
+      <c r="D232" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E231" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F231" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G231" s="3" t="s">
+      <c r="E232" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G232" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A232" s="3">
-        <f t="shared" si="3"/>
-        <v>231</v>
-      </c>
-      <c r="B232" s="3">
+    <row r="233" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="3">
+        <f>ROW()-1</f>
+        <v>232</v>
+      </c>
+      <c r="B233" s="3">
+        <v>21880</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="3">
+        <f>ROW()-1</f>
+        <v>233</v>
+      </c>
+      <c r="B234" s="3">
         <v>21883</v>
       </c>
-      <c r="C232" s="3" t="s">
+      <c r="C234" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="D232" s="3" t="s">
+      <c r="D234" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E232" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F232" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G232" s="3" t="s">
+      <c r="E234" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G234" s="3" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A233" s="3">
-        <f t="shared" si="3"/>
-        <v>232</v>
-      </c>
-      <c r="B233" s="3">
+    <row r="235" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="3">
+        <f>ROW()-1</f>
+        <v>234</v>
+      </c>
+      <c r="B235" s="3">
         <v>21888</v>
       </c>
-      <c r="C233" s="3" t="s">
+      <c r="C235" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="D233" s="3" t="s">
+      <c r="D235" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="E233" s="3" t="s">
+      <c r="E235" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F233" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G233" s="3" t="s">
+      <c r="F235" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G235" s="3" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A234" s="3">
-        <f t="shared" si="3"/>
-        <v>233</v>
-      </c>
-      <c r="B234" s="3">
+    <row r="236" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="3">
+        <f>ROW()-1</f>
+        <v>235</v>
+      </c>
+      <c r="B236" s="3">
         <v>21889</v>
       </c>
-      <c r="C234" s="3" t="s">
+      <c r="C236" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="D234" s="3" t="s">
+      <c r="D236" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E234" s="3" t="s">
+      <c r="E236" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F234" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G234" s="3" t="s">
+      <c r="F236" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G236" s="3" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A235" s="3">
-        <f>ROW()-1</f>
-        <v>234</v>
-      </c>
-      <c r="B235" s="3">
-        <v>21916</v>
-      </c>
-      <c r="C235" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E235" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F235" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G235" s="3" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A236" s="3">
-        <f>ROW()-1</f>
-        <v>235</v>
-      </c>
-      <c r="B236" s="3">
-        <v>21799</v>
-      </c>
-      <c r="C236" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E236" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F236" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G236" s="3" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="3">
         <f>ROW()-1</f>
         <v>236</v>
@@ -9784,16 +9777,16 @@
         <v>511</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
         <f>ROW()-1</f>
         <v>237</v>
       </c>
       <c r="B238" s="3">
-        <v>21880</v>
+        <v>21916</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>68</v>
@@ -9805,10 +9798,10 @@
         <v>88</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="3">
         <f>ROW()-1</f>
         <v>238</v>
@@ -9822,10 +9815,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B239">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -9837,19 +9830,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{611420FC-D4C7-424A-870C-F1AC7FD39257}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
@@ -9875,7 +9867,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="38">
         <f>ROW()-1</f>
         <v>1</v>
@@ -9902,7 +9894,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="38">
         <f>ROW()-1</f>
         <v>2</v>
@@ -9929,7 +9921,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="38">
         <f>ROW()-1</f>
         <v>3</v>
@@ -9956,7 +9948,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <f>ROW()-1</f>
         <v>4</v>
@@ -9983,7 +9975,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A6" s="38">
         <f>ROW()-1</f>
         <v>5</v>
@@ -10007,23 +9999,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5F6050-FB7D-4193-8E9E-199F19695B01}">
   <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
-    <col min="3" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="3.77734375" customWidth="1"/>
-    <col min="7" max="7" width="55.77734375" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" customWidth="1"/>
-    <col min="11" max="11" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="55.77734375" customWidth="1"/>
-    <col min="13" max="13" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
+    <col min="7" max="7" width="55.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="55.7109375" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -10050,7 +10042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <f t="shared" ref="A2:A41" si="0">ROW()-1</f>
         <v>1</v>
@@ -10083,7 +10075,7 @@
         <v>2.9535864978902954E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -10116,7 +10108,7 @@
         <v>8.4388185654008432E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -10149,7 +10141,7 @@
         <v>1.2658227848101266E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -10182,7 +10174,7 @@
         <v>0.189873417721519</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -10215,7 +10207,7 @@
         <v>2.1097046413502109E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -10248,7 +10240,7 @@
         <v>0.10548523206751055</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -10281,7 +10273,7 @@
         <v>0.63291139240506333</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -10308,7 +10300,7 @@
       </c>
       <c r="I9" s="21"/>
     </row>
-    <row r="10" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -10330,7 +10322,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -10360,7 +10352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -10392,7 +10384,7 @@
         <v>7.1729957805907171E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -10424,7 +10416,7 @@
         <v>0.92827004219409281</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -10451,7 +10443,7 @@
       </c>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -10469,7 +10461,7 @@
       </c>
       <c r="E15" s="18"/>
     </row>
-    <row r="16" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -10499,7 +10491,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -10532,7 +10524,7 @@
         <v>0.10548523206751055</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -10564,7 +10556,7 @@
         <v>9.7046413502109699E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -10596,7 +10588,7 @@
         <v>6.7510548523206745E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -10623,7 +10615,7 @@
       </c>
       <c r="I20" s="35"/>
     </row>
-    <row r="21" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -10641,7 +10633,7 @@
       </c>
       <c r="E21" s="18"/>
     </row>
-    <row r="22" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -10671,7 +10663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -10704,7 +10696,7 @@
         <v>4.2194092827004216E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -10736,7 +10728,7 @@
         <v>4.2194092827004216E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -10768,7 +10760,7 @@
         <v>4.2194092827004216E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -10795,7 +10787,7 @@
       </c>
       <c r="I26" s="35"/>
     </row>
-    <row r="27" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -10813,7 +10805,7 @@
       </c>
       <c r="E27" s="18"/>
     </row>
-    <row r="28" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -10831,7 +10823,7 @@
       </c>
       <c r="E28" s="18"/>
     </row>
-    <row r="29" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -10848,7 +10840,7 @@
         <v>2.1097046413502109E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -10865,7 +10857,7 @@
         <v>2.9535864978902954E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -10882,7 +10874,7 @@
         <v>1.6877637130801686E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -10899,7 +10891,7 @@
         <v>2.1097046413502109E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -10916,7 +10908,7 @@
         <v>1.2658227848101266E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -10933,7 +10925,7 @@
         <v>4.2194092827004218E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -10950,7 +10942,7 @@
         <v>8.4388185654008432E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -10967,7 +10959,7 @@
         <v>4.2194092827004216E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -10984,7 +10976,7 @@
         <v>3.7974683544303799E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -11001,7 +10993,7 @@
         <v>3.7974683544303799E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -11018,7 +11010,7 @@
         <v>5.0632911392405063E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -11035,7 +11027,7 @@
         <v>4.2194092827004216E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -11052,7 +11044,7 @@
         <v>9.7046413502109699E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A42" s="7"/>
       <c r="B42" s="8" t="s">
         <v>16</v>

--- a/الخدمات.xlsx
+++ b/الخدمات.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDTC\Desktop\JavaScript-codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C02B2B-39EC-44AF-80AB-B20C0F454EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFEF96A-8677-43AF-842B-B5EE3B633143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="530">
   <si>
     <t>ت.</t>
   </si>
@@ -1635,6 +1635,21 @@
   </si>
   <si>
     <t>وثيقة تخرج</t>
+  </si>
+  <si>
+    <t>أستبانة رضا الأطراف المعنية</t>
+  </si>
+  <si>
+    <t>رضا الاطراف</t>
+  </si>
+  <si>
+    <t>استمارة الترشيح لعضوية مجلس الخدمة العامة الاتحادي</t>
+  </si>
+  <si>
+    <t>مجلس الخدمة الاتحادي</t>
+  </si>
+  <si>
+    <t>ترشيح عضوية</t>
   </si>
 </sst>
 </file>
@@ -1984,7 +1999,150 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="70">
+  <dxfs count="72">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2330,38 +2488,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2388,37 +2514,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2458,37 +2553,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2520,35 +2584,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3711,64 +3746,57 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G239" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68">
-  <autoFilter ref="A1:G239" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="الهيئة الوطنية للرقابة النووية والاشعاعية والكيميائية والبايولوجية"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G241" totalsRowShown="0" headerRowDxfId="71" dataDxfId="69" headerRowBorderDxfId="70">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G239">
     <sortCondition ref="B2:B239"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{20FD99FD-87DB-4DD1-989A-014AAE8F25F6}" name="ت." dataDxfId="66" totalsRowDxfId="65">
+    <tableColumn id="1" xr3:uid="{20FD99FD-87DB-4DD1-989A-014AAE8F25F6}" name="ت." dataDxfId="68" totalsRowDxfId="67">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F323E4AC-F323-4F97-9904-326D9949B165}" name="رقم الخدمة" dataDxfId="64" totalsRowDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{58A3CC8C-66BF-4DA6-B0EF-C7F43089C5C0}" name="اسم الخدمة" dataDxfId="62" totalsRowDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{176DB514-0824-46BC-9146-CAA89D7A742F}" name="جهة الخدمة" dataDxfId="60" totalsRowDxfId="59"/>
-    <tableColumn id="5" xr3:uid="{E4173C63-A839-4611-8E53-7B3AE2F439DB}" name="نوع الجهة" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{C01A4E12-3E16-4DE9-86B3-69F70894487E}" name="نوع العمل" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{3481871F-BF9F-4C45-AC54-67A9AF362483}" name="اسم الملف" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{F323E4AC-F323-4F97-9904-326D9949B165}" name="رقم الخدمة" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{58A3CC8C-66BF-4DA6-B0EF-C7F43089C5C0}" name="اسم الخدمة" dataDxfId="64" totalsRowDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{176DB514-0824-46BC-9146-CAA89D7A742F}" name="جهة الخدمة" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{E4173C63-A839-4611-8E53-7B3AE2F439DB}" name="نوع الجهة" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{C01A4E12-3E16-4DE9-86B3-69F70894487E}" name="نوع العمل" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{3481871F-BF9F-4C45-AC54-67A9AF362483}" name="اسم الملف" dataDxfId="56" totalsRowDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{84F97999-FBC9-427B-AC68-DAFBADA61BB8}" name="Table5" displayName="Table5" ref="A1:H6" totalsRowShown="0" headerRowDxfId="52" dataDxfId="50" headerRowBorderDxfId="51" tableBorderDxfId="49" totalsRowBorderDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{84F97999-FBC9-427B-AC68-DAFBADA61BB8}" name="Table5" displayName="Table5" ref="A1:H6" totalsRowShown="0" headerRowDxfId="54" dataDxfId="52" headerRowBorderDxfId="53" tableBorderDxfId="51" totalsRowBorderDxfId="50">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{69E53D5C-73E1-4C2D-A2FF-8B09CE7A5D9B}" name="ت." dataDxfId="47">
+    <tableColumn id="1" xr3:uid="{69E53D5C-73E1-4C2D-A2FF-8B09CE7A5D9B}" name="ت." dataDxfId="49">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EBAAD0E3-6F6D-4DE2-A8C7-BC5A0EEE6FE2}" name="رقم الخدمة" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{0BCF7553-361D-472A-8D6B-445844D28E52}" name="اسم الخدمة" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{3E2F9AA3-02D8-4C6F-8CBA-BA47686A8C20}" name="جهة الخدمة" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{9F37D9B7-7A9A-4709-8DFC-E6579BBF5270}" name="نوع الجهة" dataDxfId="43"/>
-    <tableColumn id="9" xr3:uid="{2DD6D84B-0F1F-4F7E-BFC9-49CC99A8B055}" name="نوع العمل" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{97CE7C95-A47D-44C9-B115-777267316E94}" name="اسم الملف" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{2C0E9C57-3204-4A1B-B24D-2DE53DDD9D13}" name="مكان الدفع" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{EBAAD0E3-6F6D-4DE2-A8C7-BC5A0EEE6FE2}" name="رقم الخدمة" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{0BCF7553-361D-472A-8D6B-445844D28E52}" name="اسم الخدمة" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{3E2F9AA3-02D8-4C6F-8CBA-BA47686A8C20}" name="جهة الخدمة" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{9F37D9B7-7A9A-4709-8DFC-E6579BBF5270}" name="نوع الجهة" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{2DD6D84B-0F1F-4F7E-BFC9-49CC99A8B055}" name="نوع العمل" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{97CE7C95-A47D-44C9-B115-777267316E94}" name="اسم الملف" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{2C0E9C57-3204-4A1B-B24D-2DE53DDD9D13}" name="مكان الدفع" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="39" dataDxfId="37" totalsRowDxfId="36" headerRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="41" dataDxfId="39" totalsRowDxfId="38" headerRowBorderDxfId="40">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F2:I8">
     <sortCondition ref="G2:G8"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FDC31943-D832-4BCF-8A6F-51F74847839D}" name="ت." dataDxfId="35" totalsRowDxfId="34">
+    <tableColumn id="1" xr3:uid="{FDC31943-D832-4BCF-8A6F-51F74847839D}" name="ت." dataDxfId="37" totalsRowDxfId="36">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D6F61CFE-6FB5-4088-802C-280AB03DDC3F}" name="نوع الجهة" totalsRowLabel="المجموع" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{819F64F0-7B30-437C-8552-96E1BA009158}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="2" xr3:uid="{D6F61CFE-6FB5-4088-802C-280AB03DDC3F}" name="نوع الجهة" totalsRowLabel="المجموع" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{819F64F0-7B30-437C-8552-96E1BA009158}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32">
       <calculatedColumnFormula>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D928E8D0-BE48-4700-B3FA-A3A0C6ED8D95}" name="النسبة المئوية" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{D928E8D0-BE48-4700-B3FA-A3A0C6ED8D95}" name="النسبة المئوية" dataDxfId="31" totalsRowDxfId="30" dataCellStyle="Percent">
       <calculatedColumnFormula>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3777,19 +3805,19 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D42" totalsRowCount="1" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D43" totalsRowCount="1" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D41">
     <sortCondition ref="B2:B41"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{04CB5523-1DF6-4CA0-AC24-1D21F85D9F94}" name="ت." dataDxfId="22" totalsRowDxfId="21">
+    <tableColumn id="1" xr3:uid="{04CB5523-1DF6-4CA0-AC24-1D21F85D9F94}" name="ت." dataDxfId="24" totalsRowDxfId="5">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{966ACB29-C086-4C8E-BD62-D0F9ECCCA301}" name="اسم الجهة" totalsRowLabel="المجموع" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{E47A3AE0-B7A7-44F8-8FA6-8FA757A3066F}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="17">
+    <tableColumn id="2" xr3:uid="{966ACB29-C086-4C8E-BD62-D0F9ECCCA301}" name="اسم الجهة" totalsRowLabel="المجموع" dataDxfId="23" totalsRowDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{E47A3AE0-B7A7-44F8-8FA6-8FA757A3066F}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="22" totalsRowDxfId="3">
       <calculatedColumnFormula>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0D34DEDD-061D-44F4-9DA6-86D41E4BDDB7}" name="النسبة المئوية" totalsRowFunction="sum" dataDxfId="16" totalsRowDxfId="15" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{0D34DEDD-061D-44F4-9DA6-86D41E4BDDB7}" name="النسبة المئوية" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="2" dataCellStyle="Percent">
       <calculatedColumnFormula>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3798,16 +3826,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="9" totalsRowDxfId="8">
+    <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="15" totalsRowDxfId="14">
       <calculatedColumnFormula>ROW()-11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4A8E3EC9-46C6-46A2-85BB-E7D02B7ABF90}" name="نوع العمل" totalsRowLabel="المجموع" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{140AD779-6235-4A33-848F-7CF18BA55E33}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4">
+    <tableColumn id="2" xr3:uid="{4A8E3EC9-46C6-46A2-85BB-E7D02B7ABF90}" name="نوع العمل" totalsRowLabel="المجموع" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{140AD779-6235-4A33-848F-7CF18BA55E33}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="11" totalsRowDxfId="10">
       <calculatedColumnFormula>COUNTIF(Table1[نوع العمل],Table4[[#This Row],[نوع العمل]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CD921388-F9B8-4CDD-A07C-FBB8C0ABF589}" name="النسبة المئوية" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Percent">
+    <tableColumn id="4" xr3:uid="{CD921388-F9B8-4CDD-A07C-FBB8C0ABF589}" name="النسبة المئوية" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Percent">
       <calculatedColumnFormula>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4078,7 +4106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G239"/>
+  <dimension ref="A1:G241"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
@@ -4113,9 +4141,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A2:A65" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -4137,9 +4165,9 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B3" s="3">
@@ -4161,9 +4189,9 @@
         <v>382</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="3">
@@ -4185,9 +4213,9 @@
         <v>291</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="3">
@@ -4209,9 +4237,9 @@
         <v>10335</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="3">
@@ -4233,9 +4261,9 @@
         <v>312</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="3">
@@ -4257,9 +4285,9 @@
         <v>237</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="3">
@@ -4281,9 +4309,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="3">
@@ -4305,9 +4333,9 @@
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="3">
@@ -4329,9 +4357,9 @@
         <v>226</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="3">
@@ -4353,9 +4381,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="3">
@@ -4377,9 +4405,9 @@
         <v>227</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="3">
@@ -4401,9 +4429,9 @@
         <v>503</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="3">
@@ -4425,9 +4453,9 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="3">
@@ -4449,9 +4477,9 @@
         <v>481</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="3">
@@ -4475,7 +4503,7 @@
     </row>
     <row r="17" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="3">
@@ -4499,7 +4527,7 @@
     </row>
     <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="3">
@@ -4523,7 +4551,7 @@
     </row>
     <row r="19" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="3">
@@ -4545,9 +4573,9 @@
         <v>10541</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="3">
@@ -4571,7 +4599,7 @@
     </row>
     <row r="21" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" s="3">
@@ -4595,7 +4623,7 @@
     </row>
     <row r="22" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="3">
@@ -4617,9 +4645,9 @@
         <v>10568</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" s="3">
@@ -4641,9 +4669,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" s="3">
@@ -4667,7 +4695,7 @@
     </row>
     <row r="25" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" s="3">
@@ -4691,7 +4719,7 @@
     </row>
     <row r="26" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" s="3">
@@ -4713,9 +4741,9 @@
         <v>10630</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" s="3">
@@ -4737,9 +4765,9 @@
         <v>232</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="3">
@@ -4761,9 +4789,9 @@
         <v>10664</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="3">
@@ -4787,7 +4815,7 @@
     </row>
     <row r="30" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" s="3">
@@ -4809,9 +4837,9 @@
         <v>10688</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" s="3">
@@ -4833,9 +4861,9 @@
         <v>361</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="3">
@@ -4857,9 +4885,9 @@
         <v>238</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33" s="3">
@@ -4881,9 +4909,9 @@
         <v>163</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" s="3">
@@ -4905,9 +4933,9 @@
         <v>363</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B35" s="3">
@@ -4929,9 +4957,9 @@
         <v>404</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B36" s="3">
@@ -4953,9 +4981,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B37" s="3">
@@ -4977,9 +5005,9 @@
         <v>321</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B38" s="3">
@@ -5001,9 +5029,9 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B39" s="3">
@@ -5025,9 +5053,9 @@
         <v>262</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B40" s="3">
@@ -5051,7 +5079,7 @@
     </row>
     <row r="41" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B41" s="3">
@@ -5073,9 +5101,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B42" s="3">
@@ -5097,9 +5125,9 @@
         <v>234</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B43" s="3">
@@ -5121,9 +5149,9 @@
         <v>376</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B44" s="3">
@@ -5145,9 +5173,9 @@
         <v>215</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B45" s="3">
@@ -5169,9 +5197,9 @@
         <v>261</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B46" s="3">
@@ -5193,9 +5221,9 @@
         <v>170</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B47" s="3">
@@ -5217,9 +5245,9 @@
         <v>171</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B48" s="3">
@@ -5241,9 +5269,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B49" s="3">
@@ -5265,9 +5293,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B50" s="3">
@@ -5289,9 +5317,9 @@
         <v>193</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B51" s="3">
@@ -5313,9 +5341,9 @@
         <v>172</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B52" s="3">
@@ -5337,9 +5365,9 @@
         <v>197</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B53" s="3">
@@ -5361,9 +5389,9 @@
         <v>174</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B54" s="3">
@@ -5385,9 +5413,9 @@
         <v>201</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B55" s="3">
@@ -5411,7 +5439,7 @@
     </row>
     <row r="56" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B56" s="3">
@@ -5433,9 +5461,9 @@
         <v>21076</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B57" s="3">
@@ -5457,9 +5485,9 @@
         <v>179</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B58" s="3">
@@ -5481,9 +5509,9 @@
         <v>218</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B59" s="3">
@@ -5505,9 +5533,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B60" s="3">
@@ -5529,9 +5557,9 @@
         <v>302</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B61" s="3">
@@ -5553,9 +5581,9 @@
         <v>229</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B62" s="3">
@@ -5577,9 +5605,9 @@
         <v>267</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="B63" s="3">
@@ -5601,9 +5629,9 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B64" s="3">
@@ -5625,9 +5653,9 @@
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B65" s="3">
@@ -5649,9 +5677,9 @@
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A66:A129" si="1">ROW()-1</f>
         <v>65</v>
       </c>
       <c r="B66" s="3">
@@ -5673,9 +5701,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
       <c r="B67" s="3">
@@ -5697,9 +5725,9 @@
         <v>258</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
       <c r="B68" s="3">
@@ -5723,7 +5751,7 @@
     </row>
     <row r="69" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="B69" s="3">
@@ -5745,9 +5773,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>69</v>
       </c>
       <c r="B70" s="3">
@@ -5769,9 +5797,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="B71" s="3">
@@ -5793,9 +5821,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>71</v>
       </c>
       <c r="B72" s="3">
@@ -5817,9 +5845,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="B73" s="3">
@@ -5841,9 +5869,9 @@
         <v>437</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="B74" s="3">
@@ -5865,9 +5893,9 @@
         <v>168</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="B75" s="3">
@@ -5889,9 +5917,9 @@
         <v>259</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="B76" s="3">
@@ -5913,9 +5941,9 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="B77" s="3">
@@ -5937,9 +5965,9 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="B78" s="3">
@@ -5961,9 +5989,9 @@
         <v>256</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="B79" s="3">
@@ -5985,9 +6013,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>79</v>
       </c>
       <c r="B80" s="3">
@@ -6009,9 +6037,9 @@
         <v>252</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="B81" s="3">
@@ -6033,9 +6061,9 @@
         <v>176</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>81</v>
       </c>
       <c r="B82" s="3">
@@ -6057,9 +6085,9 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="B83" s="3">
@@ -6081,9 +6109,9 @@
         <v>285</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>83</v>
       </c>
       <c r="B84" s="3">
@@ -6105,9 +6133,9 @@
         <v>183</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="B85" s="3">
@@ -6129,9 +6157,9 @@
         <v>220</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="B86" s="3">
@@ -6153,9 +6181,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="B87" s="3">
@@ -6177,9 +6205,9 @@
         <v>245</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>87</v>
       </c>
       <c r="B88" s="3">
@@ -6201,9 +6229,9 @@
         <v>298</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="B89" s="3">
@@ -6225,9 +6253,9 @@
         <v>296</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="B90" s="3">
@@ -6249,9 +6277,9 @@
         <v>178</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="B91" s="3">
@@ -6273,9 +6301,9 @@
         <v>270</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>91</v>
       </c>
       <c r="B92" s="3">
@@ -6297,9 +6325,9 @@
         <v>265</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="B93" s="3">
@@ -6321,9 +6349,9 @@
         <v>355</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>93</v>
       </c>
       <c r="B94" s="3">
@@ -6345,9 +6373,9 @@
         <v>257</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="B95" s="3">
@@ -6369,9 +6397,9 @@
         <v>264</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="B96" s="3">
@@ -6393,9 +6421,9 @@
         <v>202</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="B97" s="3">
@@ -6417,9 +6445,9 @@
         <v>253</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="B98" s="3">
@@ -6441,9 +6469,9 @@
         <v>195</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>98</v>
       </c>
       <c r="B99" s="3">
@@ -6465,9 +6493,9 @@
         <v>230</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="B100" s="3">
@@ -6489,9 +6517,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="B101" s="3">
@@ -6513,9 +6541,9 @@
         <v>222</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>101</v>
       </c>
       <c r="B102" s="3">
@@ -6537,9 +6565,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>102</v>
       </c>
       <c r="B103" s="3">
@@ -6561,9 +6589,9 @@
         <v>254</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>103</v>
       </c>
       <c r="B104" s="3">
@@ -6585,9 +6613,9 @@
         <v>181</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="B105" s="3">
@@ -6609,9 +6637,9 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="B106" s="3">
@@ -6633,9 +6661,9 @@
         <v>339</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>106</v>
       </c>
       <c r="B107" s="3">
@@ -6657,9 +6685,9 @@
         <v>203</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>107</v>
       </c>
       <c r="B108" s="3">
@@ -6681,9 +6709,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
       <c r="B109" s="3">
@@ -6705,9 +6733,9 @@
         <v>443</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>109</v>
       </c>
       <c r="B110" s="3">
@@ -6729,9 +6757,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="B111" s="3">
@@ -6753,9 +6781,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="B112" s="3">
@@ -6777,9 +6805,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="B113" s="3">
@@ -6801,9 +6829,9 @@
         <v>190</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>113</v>
       </c>
       <c r="B114" s="3">
@@ -6825,9 +6853,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>114</v>
       </c>
       <c r="B115" s="3">
@@ -6849,9 +6877,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="B116" s="3">
@@ -6873,9 +6901,9 @@
         <v>217</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>116</v>
       </c>
       <c r="B117" s="3">
@@ -6897,9 +6925,9 @@
         <v>216</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>117</v>
       </c>
       <c r="B118" s="3">
@@ -6921,9 +6949,9 @@
         <v>213</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>118</v>
       </c>
       <c r="B119" s="3">
@@ -6945,9 +6973,9 @@
         <v>182</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>119</v>
       </c>
       <c r="B120" s="3">
@@ -6969,9 +6997,9 @@
         <v>196</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="B121" s="3">
@@ -6993,9 +7021,9 @@
         <v>157</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>121</v>
       </c>
       <c r="B122" s="3">
@@ -7017,9 +7045,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>122</v>
       </c>
       <c r="B123" s="3">
@@ -7041,9 +7069,9 @@
         <v>315</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>123</v>
       </c>
       <c r="B124" s="3">
@@ -7065,9 +7093,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>124</v>
       </c>
       <c r="B125" s="3">
@@ -7089,9 +7117,9 @@
         <v>191</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>125</v>
       </c>
       <c r="B126" s="3">
@@ -7113,9 +7141,9 @@
         <v>241</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="B127" s="3">
@@ -7137,9 +7165,9 @@
         <v>263</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="B128" s="3">
@@ -7161,9 +7189,9 @@
         <v>418</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>128</v>
       </c>
       <c r="B129" s="3">
@@ -7185,9 +7213,9 @@
         <v>414</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A130:A193" si="2">ROW()-1</f>
         <v>129</v>
       </c>
       <c r="B130" s="3">
@@ -7209,9 +7237,9 @@
         <v>406</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>130</v>
       </c>
       <c r="B131" s="3">
@@ -7233,9 +7261,9 @@
         <v>244</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>131</v>
       </c>
       <c r="B132" s="3">
@@ -7257,9 +7285,9 @@
         <v>169</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>132</v>
       </c>
       <c r="B133" s="3">
@@ -7281,9 +7309,9 @@
         <v>243</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>133</v>
       </c>
       <c r="B134" s="3">
@@ -7305,9 +7333,9 @@
         <v>408</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>134</v>
       </c>
       <c r="B135" s="3">
@@ -7329,9 +7357,9 @@
         <v>410</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>135</v>
       </c>
       <c r="B136" s="3">
@@ -7353,9 +7381,9 @@
         <v>416</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>136</v>
       </c>
       <c r="B137" s="3">
@@ -7377,9 +7405,9 @@
         <v>248</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="B138" s="3">
@@ -7401,9 +7429,9 @@
         <v>247</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>138</v>
       </c>
       <c r="B139" s="3">
@@ -7425,9 +7453,9 @@
         <v>209</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>139</v>
       </c>
       <c r="B140" s="3">
@@ -7449,9 +7477,9 @@
         <v>158</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>140</v>
       </c>
       <c r="B141" s="3">
@@ -7473,9 +7501,9 @@
         <v>214</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>141</v>
       </c>
       <c r="B142" s="3">
@@ -7497,9 +7525,9 @@
         <v>412</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>142</v>
       </c>
       <c r="B143" s="3">
@@ -7521,9 +7549,9 @@
         <v>223</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>143</v>
       </c>
       <c r="B144" s="3">
@@ -7545,9 +7573,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>144</v>
       </c>
       <c r="B145" s="3">
@@ -7569,9 +7597,9 @@
         <v>332</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>145</v>
       </c>
       <c r="B146" s="3">
@@ -7593,9 +7621,9 @@
         <v>330</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>146</v>
       </c>
       <c r="B147" s="3">
@@ -7617,9 +7645,9 @@
         <v>473</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>147</v>
       </c>
       <c r="B148" s="3">
@@ -7641,9 +7669,9 @@
         <v>219</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>148</v>
       </c>
       <c r="B149" s="3">
@@ -7665,9 +7693,9 @@
         <v>400</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>149</v>
       </c>
       <c r="B150" s="3">
@@ -7689,9 +7717,9 @@
         <v>475</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="B151" s="3">
@@ -7713,9 +7741,9 @@
         <v>287</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>151</v>
       </c>
       <c r="B152" s="3">
@@ -7737,9 +7765,9 @@
         <v>224</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>152</v>
       </c>
       <c r="B153" s="3">
@@ -7761,9 +7789,9 @@
         <v>335</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>153</v>
       </c>
       <c r="B154" s="3">
@@ -7785,9 +7813,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>154</v>
       </c>
       <c r="B155" s="3">
@@ -7809,9 +7837,9 @@
         <v>398</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>155</v>
       </c>
       <c r="B156" s="3">
@@ -7833,9 +7861,9 @@
         <v>396</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A157" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>156</v>
       </c>
       <c r="B157" s="3">
@@ -7857,9 +7885,9 @@
         <v>394</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>157</v>
       </c>
       <c r="B158" s="3">
@@ -7881,9 +7909,9 @@
         <v>274</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>158</v>
       </c>
       <c r="B159" s="3">
@@ -7905,9 +7933,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>159</v>
       </c>
       <c r="B160" s="3">
@@ -7929,9 +7957,9 @@
         <v>402</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="B161" s="3">
@@ -7955,7 +7983,7 @@
     </row>
     <row r="162" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>161</v>
       </c>
       <c r="B162" s="3">
@@ -7977,9 +8005,9 @@
         <v>21612</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A163" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>162</v>
       </c>
       <c r="B163" s="3">
@@ -8001,9 +8029,9 @@
         <v>389</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>163</v>
       </c>
       <c r="B164" s="3">
@@ -8025,9 +8053,9 @@
         <v>387</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A165" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>164</v>
       </c>
       <c r="B165" s="3">
@@ -8049,9 +8077,9 @@
         <v>392</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>165</v>
       </c>
       <c r="B166" s="3">
@@ -8073,9 +8101,9 @@
         <v>384</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A167" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>166</v>
       </c>
       <c r="B167" s="3">
@@ -8097,9 +8125,9 @@
         <v>465</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>167</v>
       </c>
       <c r="B168" s="3">
@@ -8123,7 +8151,7 @@
     </row>
     <row r="169" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>168</v>
       </c>
       <c r="B169" s="3">
@@ -8145,9 +8173,9 @@
         <v>21626</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>169</v>
       </c>
       <c r="B170" s="3">
@@ -8169,9 +8197,9 @@
         <v>370</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A171" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>170</v>
       </c>
       <c r="B171" s="3">
@@ -8195,7 +8223,7 @@
     </row>
     <row r="172" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>171</v>
       </c>
       <c r="B172" s="3">
@@ -8217,9 +8245,9 @@
         <v>21633</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A173" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>172</v>
       </c>
       <c r="B173" s="3">
@@ -8241,9 +8269,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>173</v>
       </c>
       <c r="B174" s="3">
@@ -8265,9 +8293,9 @@
         <v>281</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>174</v>
       </c>
       <c r="B175" s="3">
@@ -8289,9 +8317,9 @@
         <v>251</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>175</v>
       </c>
       <c r="B176" s="3">
@@ -8313,9 +8341,9 @@
         <v>327</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>176</v>
       </c>
       <c r="B177" s="3">
@@ -8337,9 +8365,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>177</v>
       </c>
       <c r="B178" s="3">
@@ -8361,9 +8389,9 @@
         <v>344</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>178</v>
       </c>
       <c r="B179" s="3">
@@ -8385,9 +8413,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>179</v>
       </c>
       <c r="B180" s="3">
@@ -8409,9 +8437,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A181" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>180</v>
       </c>
       <c r="B181" s="3">
@@ -8433,9 +8461,9 @@
         <v>308</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>181</v>
       </c>
       <c r="B182" s="3">
@@ -8457,9 +8485,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A183" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>182</v>
       </c>
       <c r="B183" s="3">
@@ -8483,7 +8511,7 @@
     </row>
     <row r="184" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>183</v>
       </c>
       <c r="B184" s="3">
@@ -8507,7 +8535,7 @@
     </row>
     <row r="185" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A185" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>184</v>
       </c>
       <c r="B185" s="3">
@@ -8529,9 +8557,9 @@
         <v>21695</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>185</v>
       </c>
       <c r="B186" s="3">
@@ -8553,9 +8581,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A187" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>186</v>
       </c>
       <c r="B187" s="3">
@@ -8577,9 +8605,9 @@
         <v>459</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>187</v>
       </c>
       <c r="B188" s="3">
@@ -8601,9 +8629,9 @@
         <v>457</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A189" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>188</v>
       </c>
       <c r="B189" s="3">
@@ -8625,9 +8653,9 @@
         <v>350</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>189</v>
       </c>
       <c r="B190" s="3">
@@ -8649,9 +8677,9 @@
         <v>499</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A191" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="B191" s="3">
@@ -8673,9 +8701,9 @@
         <v>368</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>191</v>
       </c>
       <c r="B192" s="3">
@@ -8697,9 +8725,9 @@
         <v>317</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A193" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>192</v>
       </c>
       <c r="B193" s="3">
@@ -8721,9 +8749,9 @@
         <v>337</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A194:A239" si="3">ROW()-1</f>
         <v>193</v>
       </c>
       <c r="B194" s="3">
@@ -8745,9 +8773,9 @@
         <v>433</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A195" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>194</v>
       </c>
       <c r="B195" s="3">
@@ -8769,9 +8797,9 @@
         <v>348</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>195</v>
       </c>
       <c r="B196" s="3">
@@ -8793,9 +8821,9 @@
         <v>323</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A197" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>196</v>
       </c>
       <c r="B197" s="3">
@@ -8817,9 +8845,9 @@
         <v>352</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>197</v>
       </c>
       <c r="B198" s="3">
@@ -8841,9 +8869,9 @@
         <v>467</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A199" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>198</v>
       </c>
       <c r="B199" s="3">
@@ -8865,9 +8893,9 @@
         <v>492</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>199</v>
       </c>
       <c r="B200" s="3">
@@ -8889,9 +8917,9 @@
         <v>491</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A201" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="B201" s="3">
@@ -8913,9 +8941,9 @@
         <v>469</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A202" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>201</v>
       </c>
       <c r="B202" s="3">
@@ -8937,9 +8965,9 @@
         <v>422</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A203" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>202</v>
       </c>
       <c r="B203" s="3">
@@ -8961,9 +8989,9 @@
         <v>357</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A204" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>203</v>
       </c>
       <c r="B204" s="3">
@@ -8985,9 +9013,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A205" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>204</v>
       </c>
       <c r="B205" s="3">
@@ -9009,9 +9037,9 @@
         <v>495</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>205</v>
       </c>
       <c r="B206" s="3">
@@ -9033,9 +9061,9 @@
         <v>359</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A207" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>206</v>
       </c>
       <c r="B207" s="3">
@@ -9057,9 +9085,9 @@
         <v>483</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A208" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>207</v>
       </c>
       <c r="B208" s="3">
@@ -9081,9 +9109,9 @@
         <v>447</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A209" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>208</v>
       </c>
       <c r="B209" s="3">
@@ -9105,9 +9133,9 @@
         <v>489</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>209</v>
       </c>
       <c r="B210" s="3">
@@ -9129,9 +9157,9 @@
         <v>380</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A211" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>210</v>
       </c>
       <c r="B211" s="3">
@@ -9153,9 +9181,9 @@
         <v>428</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A212" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>211</v>
       </c>
       <c r="B212" s="3">
@@ -9177,9 +9205,9 @@
         <v>461</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A213" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>212</v>
       </c>
       <c r="B213" s="3">
@@ -9201,9 +9229,9 @@
         <v>374</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>213</v>
       </c>
       <c r="B214" s="3">
@@ -9225,9 +9253,9 @@
         <v>455</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A215" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>214</v>
       </c>
       <c r="B215" s="3">
@@ -9249,9 +9277,9 @@
         <v>365</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>215</v>
       </c>
       <c r="B216" s="3">
@@ -9273,9 +9301,9 @@
         <v>509</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A217" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>216</v>
       </c>
       <c r="B217" s="3">
@@ -9297,9 +9325,9 @@
         <v>449</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A218" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>217</v>
       </c>
       <c r="B218" s="3">
@@ -9321,9 +9349,9 @@
         <v>378</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A219" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>218</v>
       </c>
       <c r="B219" s="3">
@@ -9345,9 +9373,9 @@
         <v>463</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A220" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>219</v>
       </c>
       <c r="B220" s="3">
@@ -9369,9 +9397,9 @@
         <v>426</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A221" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>220</v>
       </c>
       <c r="B221" s="3">
@@ -9393,9 +9421,9 @@
         <v>420</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A222" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>221</v>
       </c>
       <c r="B222" s="3">
@@ -9417,9 +9445,9 @@
         <v>441</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A223" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>222</v>
       </c>
       <c r="B223" s="3">
@@ -9441,9 +9469,9 @@
         <v>431</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>223</v>
       </c>
       <c r="B224" s="3">
@@ -9465,9 +9493,9 @@
         <v>424</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A225" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>224</v>
       </c>
       <c r="B225" s="3">
@@ -9489,9 +9517,9 @@
         <v>451</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A226" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>225</v>
       </c>
       <c r="B226" s="3">
@@ -9513,9 +9541,9 @@
         <v>497</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A227" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>226</v>
       </c>
       <c r="B227" s="3">
@@ -9537,9 +9565,9 @@
         <v>439</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A228" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>227</v>
       </c>
       <c r="B228" s="3">
@@ -9561,9 +9589,9 @@
         <v>435</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A229" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>228</v>
       </c>
       <c r="B229" s="3">
@@ -9585,9 +9613,9 @@
         <v>479</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A230" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>229</v>
       </c>
       <c r="B230" s="3">
@@ -9609,9 +9637,9 @@
         <v>471</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A231" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>230</v>
       </c>
       <c r="B231" s="3">
@@ -9633,9 +9661,9 @@
         <v>453</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A232" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>231</v>
       </c>
       <c r="B232" s="3">
@@ -9657,9 +9685,9 @@
         <v>485</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A233" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>232</v>
       </c>
       <c r="B233" s="3">
@@ -9681,9 +9709,9 @@
         <v>524</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A234" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>233</v>
       </c>
       <c r="B234" s="3">
@@ -9705,9 +9733,9 @@
         <v>487</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A235" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>234</v>
       </c>
       <c r="B235" s="3">
@@ -9729,9 +9757,9 @@
         <v>501</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A236" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>235</v>
       </c>
       <c r="B236" s="3">
@@ -9753,9 +9781,9 @@
         <v>505</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A237" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>236</v>
       </c>
       <c r="B237" s="3">
@@ -9777,9 +9805,9 @@
         <v>511</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>237</v>
       </c>
       <c r="B238" s="3">
@@ -9801,23 +9829,71 @@
         <v>507</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A239" s="3">
+        <f t="shared" si="3"/>
+        <v>238</v>
+      </c>
+      <c r="B239" s="3">
+        <v>21913</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A240" s="3">
         <f>ROW()-1</f>
-        <v>238</v>
-      </c>
-      <c r="B239" s="3"/>
-      <c r="C239" s="3"/>
-      <c r="D239" s="3"/>
-      <c r="E239" s="3"/>
-      <c r="F239" s="3"/>
-      <c r="G239" s="3"/>
+        <v>239</v>
+      </c>
+      <c r="B240" s="3">
+        <v>10549</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A241" s="3">
+        <f>ROW()-1</f>
+        <v>240</v>
+      </c>
+      <c r="B241" s="3"/>
+      <c r="C241" s="3"/>
+      <c r="D241" s="3"/>
+      <c r="E241" s="3"/>
+      <c r="F241" s="3"/>
+      <c r="G241" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B239">
+  <conditionalFormatting sqref="B2:B241">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9998,7 +10074,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5F6050-FB7D-4193-8E9E-199F19695B01}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
@@ -10006,7 +10082,7 @@
     <col min="3" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="8.85546875" customWidth="1"/>
     <col min="6" max="6" width="3.7109375" customWidth="1"/>
-    <col min="7" max="7" width="55.7109375" customWidth="1"/>
+    <col min="7" max="7" width="59.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" customWidth="1"/>
@@ -10056,7 +10132,7 @@
       </c>
       <c r="D2" s="23">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.368200836820083E-3</v>
       </c>
       <c r="E2" s="18"/>
       <c r="F2" s="25">
@@ -10072,7 +10148,7 @@
       </c>
       <c r="I2" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>2.9535864978902954E-2</v>
+        <v>2.9288702928870293E-2</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10089,7 +10165,7 @@
       </c>
       <c r="D3" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.5316455696202531E-2</v>
+        <v>2.5104602510460251E-2</v>
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="25">
@@ -10105,7 +10181,7 @@
       </c>
       <c r="I3" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.368200836820083E-3</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10122,7 +10198,7 @@
       </c>
       <c r="D4" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>6.7510548523206745E-2</v>
+        <v>6.6945606694560664E-2</v>
       </c>
       <c r="E4" s="18"/>
       <c r="F4" s="25">
@@ -10134,11 +10210,11 @@
       </c>
       <c r="H4" s="2">
         <f>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2658227848101266E-2</v>
+        <v>1.6736401673640166E-2</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10155,7 +10231,7 @@
       </c>
       <c r="D5" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.368200836820083E-3</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="25">
@@ -10171,7 +10247,7 @@
       </c>
       <c r="I5" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.189873417721519</v>
+        <v>0.18828451882845187</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10188,7 +10264,7 @@
       </c>
       <c r="D6" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1097046413502109E-2</v>
+        <v>2.0920502092050208E-2</v>
       </c>
       <c r="E6" s="18"/>
       <c r="F6" s="25">
@@ -10204,7 +10280,7 @@
       </c>
       <c r="I6" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1097046413502109E-2</v>
+        <v>2.0920502092050208E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10221,7 +10297,7 @@
       </c>
       <c r="D7" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2658227848101266E-2</v>
+        <v>1.2552301255230125E-2</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="7">
@@ -10237,7 +10313,7 @@
       </c>
       <c r="I7" s="19">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.10548523206751055</v>
+        <v>0.10460251046025104</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10254,7 +10330,7 @@
       </c>
       <c r="D8" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2194092827004216E-3</v>
+        <v>4.1841004184100415E-3</v>
       </c>
       <c r="E8" s="18"/>
       <c r="F8" s="7">
@@ -10266,11 +10342,11 @@
       </c>
       <c r="H8" s="8">
         <f>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</f>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I8" s="19">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.63291139240506333</v>
+        <v>0.63179916317991636</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10287,7 +10363,7 @@
       </c>
       <c r="D9" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2194092827004216E-3</v>
+        <v>4.1841004184100415E-3</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="26"/>
@@ -10296,7 +10372,7 @@
       </c>
       <c r="H9" s="17">
         <f>SUBTOTAL(109,Table2[عدد الخدمات])</f>
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I9" s="21"/>
     </row>
@@ -10314,7 +10390,7 @@
       </c>
       <c r="D10" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>5.4852320675105488E-2</v>
+        <v>5.4393305439330547E-2</v>
       </c>
       <c r="E10" s="18"/>
       <c r="F10" s="25"/>
@@ -10336,7 +10412,7 @@
       </c>
       <c r="D11" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.368200836820083E-3</v>
       </c>
       <c r="E11" s="18"/>
       <c r="F11" s="9" t="s">
@@ -10366,7 +10442,7 @@
       </c>
       <c r="D12" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.368200836820083E-3</v>
       </c>
       <c r="E12" s="18"/>
       <c r="F12" s="12">
@@ -10381,7 +10457,7 @@
       </c>
       <c r="I12" s="15">
         <f>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</f>
-        <v>7.1729957805907171E-2</v>
+        <v>7.1129707112970716E-2</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
@@ -10398,7 +10474,7 @@
       </c>
       <c r="D13" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2658227848101266E-2</v>
+        <v>1.2552301255230125E-2</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="12">
@@ -10409,11 +10485,11 @@
       </c>
       <c r="H13" s="13">
         <f>COUNTIF(Table1[نوع العمل],Table4[[#This Row],[نوع العمل]])</f>
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I13" s="15">
         <f>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</f>
-        <v>0.92827004219409281</v>
+        <v>0.92887029288702927</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
@@ -10430,7 +10506,7 @@
       </c>
       <c r="D14" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.368200836820083E-3</v>
       </c>
       <c r="E14" s="18"/>
       <c r="F14" s="12"/>
@@ -10439,7 +10515,7 @@
       </c>
       <c r="H14" s="13">
         <f>SUBTOTAL(109,Table4[عدد الخدمات])</f>
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I14" s="14"/>
     </row>
@@ -10457,7 +10533,7 @@
       </c>
       <c r="D15" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2194092827004216E-3</v>
+        <v>4.1841004184100415E-3</v>
       </c>
       <c r="E15" s="18"/>
     </row>
@@ -10475,7 +10551,7 @@
       </c>
       <c r="D16" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>6.7510548523206745E-2</v>
+        <v>6.6945606694560664E-2</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="27" t="s">
@@ -10505,7 +10581,7 @@
       </c>
       <c r="D17" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2194092827004216E-3</v>
+        <v>4.1841004184100415E-3</v>
       </c>
       <c r="E17" s="18"/>
       <c r="F17" s="29">
@@ -10521,7 +10597,7 @@
       </c>
       <c r="I17" s="32">
         <f>H17/SUM(Table3[عدد الخدمات])</f>
-        <v>0.10548523206751055</v>
+        <v>0.10460251046025104</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10538,7 +10614,7 @@
       </c>
       <c r="D18" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2658227848101266E-2</v>
+        <v>1.2552301255230125E-2</v>
       </c>
       <c r="E18" s="18"/>
       <c r="F18" s="29">
@@ -10549,11 +10625,11 @@
         <v>وزارة الهجرة والمهجرين</v>
       </c>
       <c r="H18" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" s="16">
         <f>H18/SUM(Table3[عدد الخدمات])</f>
-        <v>9.7046413502109699E-2</v>
+        <v>0.100418410041841</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10570,7 +10646,7 @@
       </c>
       <c r="D19" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1097046413502109E-2</v>
+        <v>2.0920502092050208E-2</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="29">
@@ -10585,7 +10661,7 @@
       </c>
       <c r="I19" s="32">
         <f>H19/SUM(Table3[عدد الخدمات])</f>
-        <v>6.7510548523206745E-2</v>
+        <v>6.6945606694560664E-2</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10602,7 +10678,7 @@
       </c>
       <c r="D20" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2194092827004216E-3</v>
+        <v>4.1841004184100415E-3</v>
       </c>
       <c r="E20" s="18"/>
       <c r="F20" s="33"/>
@@ -10611,7 +10687,7 @@
       </c>
       <c r="H20" s="34">
         <f>SUM(H17:H19)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I20" s="35"/>
     </row>
@@ -10629,7 +10705,7 @@
       </c>
       <c r="D21" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.368200836820083E-3</v>
       </c>
       <c r="E21" s="18"/>
     </row>
@@ -10647,7 +10723,7 @@
       </c>
       <c r="D22" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.368200836820083E-3</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="27" t="s">
@@ -10677,7 +10753,7 @@
       </c>
       <c r="D23" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.9535864978902954E-2</v>
+        <v>2.9288702928870293E-2</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="29">
@@ -10693,7 +10769,7 @@
       </c>
       <c r="I23" s="32">
         <f>H23/SUM(Table3[عدد الخدمات])</f>
-        <v>4.2194092827004216E-3</v>
+        <v>4.1841004184100415E-3</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10710,7 +10786,7 @@
       </c>
       <c r="D24" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.5316455696202531E-2</v>
+        <v>2.5104602510460251E-2</v>
       </c>
       <c r="E24" s="18"/>
       <c r="F24" s="29">
@@ -10725,7 +10801,7 @@
       </c>
       <c r="I24" s="16">
         <f>H24/SUM(Table3[عدد الخدمات])</f>
-        <v>4.2194092827004216E-3</v>
+        <v>4.1841004184100415E-3</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10742,7 +10818,7 @@
       </c>
       <c r="D25" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.7974683544303799E-2</v>
+        <v>3.7656903765690378E-2</v>
       </c>
       <c r="E25" s="18"/>
       <c r="F25" s="29">
@@ -10757,7 +10833,7 @@
       </c>
       <c r="I25" s="32">
         <f>H25/SUM(Table3[عدد الخدمات])</f>
-        <v>4.2194092827004216E-3</v>
+        <v>4.1841004184100415E-3</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10774,7 +10850,7 @@
       </c>
       <c r="D26" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>0.10548523206751055</v>
+        <v>0.10460251046025104</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="33"/>
@@ -10801,7 +10877,7 @@
       </c>
       <c r="D27" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2194092827004216E-3</v>
+        <v>4.1841004184100415E-3</v>
       </c>
       <c r="E27" s="18"/>
     </row>
@@ -10819,7 +10895,7 @@
       </c>
       <c r="D28" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.7974683544303799E-2</v>
+        <v>3.7656903765690378E-2</v>
       </c>
       <c r="E28" s="18"/>
     </row>
@@ -10837,7 +10913,7 @@
       </c>
       <c r="D29" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1097046413502109E-2</v>
+        <v>2.0920502092050208E-2</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10854,7 +10930,7 @@
       </c>
       <c r="D30" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.9535864978902954E-2</v>
+        <v>2.9288702928870293E-2</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10871,7 +10947,7 @@
       </c>
       <c r="D31" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.6877637130801686E-2</v>
+        <v>1.6736401673640166E-2</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
@@ -10888,7 +10964,7 @@
       </c>
       <c r="D32" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.1097046413502109E-2</v>
+        <v>2.0920502092050208E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -10905,7 +10981,7 @@
       </c>
       <c r="D33" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.2658227848101266E-2</v>
+        <v>1.2552301255230125E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -10922,7 +10998,7 @@
       </c>
       <c r="D34" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2194092827004218E-2</v>
+        <v>4.1841004184100417E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -10939,7 +11015,7 @@
       </c>
       <c r="D35" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.368200836820083E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -10956,7 +11032,7 @@
       </c>
       <c r="D36" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2194092827004216E-3</v>
+        <v>4.1841004184100415E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -10973,7 +11049,7 @@
       </c>
       <c r="D37" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.7974683544303799E-2</v>
+        <v>3.7656903765690378E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -10990,7 +11066,7 @@
       </c>
       <c r="D38" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.7974683544303799E-2</v>
+        <v>3.7656903765690378E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -11007,7 +11083,7 @@
       </c>
       <c r="D39" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>5.0632911392405063E-2</v>
+        <v>5.0209205020920501E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -11024,7 +11100,7 @@
       </c>
       <c r="D40" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.2194092827004216E-3</v>
+        <v>4.1841004184100415E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -11037,25 +11113,42 @@
       </c>
       <c r="C41" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D41" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.7046413502109699E-2</v>
+        <v>0.100418410041841</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
+      <c r="A42" s="8">
+        <f>ROW()-1</f>
+        <v>41</v>
+      </c>
       <c r="B42" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="C42" s="8">
+        <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
+        <v>1</v>
+      </c>
+      <c r="D42" s="19">
+        <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
+        <v>4.1841004184100415E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="7"/>
+      <c r="B43" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="8">
+      <c r="C43" s="8">
         <f>SUBTOTAL(109,Table3[عدد الخدمات])</f>
-        <v>237</v>
-      </c>
-      <c r="D42" s="20">
+        <v>239</v>
+      </c>
+      <c r="D43" s="20">
         <f>SUBTOTAL(109,Table3[النسبة المئوية])</f>
-        <v>0.99999999999999989</v>
+        <v>1.0000000000000002</v>
       </c>
     </row>
   </sheetData>
